--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_RMSEP.xlsx
@@ -214,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,13 +230,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -246,12 +239,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -263,49 +271,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -670,52 +641,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>461.51538055641498</v>
+        <v>460.77347334420813</v>
       </c>
       <c r="C2">
-        <v>544.259175320601</v>
+        <v>543.84610505803425</v>
       </c>
       <c r="D2">
-        <v>472.27716447203301</v>
+        <v>471.78719021186203</v>
       </c>
       <c r="E2">
-        <v>455.93764856079071</v>
+        <v>454.54624682009592</v>
       </c>
       <c r="F2">
-        <v>435.21690923292749</v>
+        <v>433.44880101827192</v>
       </c>
       <c r="G2">
-        <v>428.65838476310802</v>
+        <v>428.46666602838491</v>
       </c>
       <c r="H2">
-        <v>415.96055395544761</v>
+        <v>415.33408947654141</v>
       </c>
       <c r="I2">
-        <v>412.87637900368748</v>
+        <v>411.34693653213321</v>
       </c>
       <c r="J2">
-        <v>420.01392477912538</v>
+        <v>417.472216221304</v>
       </c>
       <c r="K2">
-        <v>431.24081281935662</v>
+        <v>430.8956080698357</v>
       </c>
       <c r="L2">
-        <v>446.76804050206312</v>
+        <v>445.65025982064941</v>
       </c>
       <c r="M2">
-        <v>442.14250171178281</v>
+        <v>441.31009544138681</v>
       </c>
       <c r="N2">
-        <v>459.78487896775027</v>
+        <v>461.13927668141088</v>
       </c>
       <c r="O2">
-        <v>474.34159778241548</v>
+        <v>473.97910630958302</v>
       </c>
       <c r="P2">
-        <v>476.65617948141659</v>
+        <v>474.07314912121592</v>
       </c>
       <c r="Q2">
-        <v>465.77697761938492</v>
+        <v>465.38693200551501</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -723,52 +694,52 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>479.45634334397351</v>
+        <v>479.79797402406712</v>
       </c>
       <c r="C3">
-        <v>509.92907286996223</v>
+        <v>509.06114048037398</v>
       </c>
       <c r="D3">
-        <v>464.3619332069706</v>
+        <v>463.49719915012668</v>
       </c>
       <c r="E3">
-        <v>461.9907916856472</v>
+        <v>460.37040616812408</v>
       </c>
       <c r="F3">
-        <v>457.61806377823672</v>
+        <v>460.5634245246095</v>
       </c>
       <c r="G3">
-        <v>469.84345021259219</v>
+        <v>471.18548967130431</v>
       </c>
       <c r="H3">
-        <v>471.19735648783143</v>
+        <v>473.83833353427349</v>
       </c>
       <c r="I3">
-        <v>495.07530079062781</v>
+        <v>498.37147808557899</v>
       </c>
       <c r="J3">
-        <v>501.50282892633589</v>
+        <v>505.44823206382148</v>
       </c>
       <c r="K3">
-        <v>509.65002980201672</v>
+        <v>513.82086534592679</v>
       </c>
       <c r="L3">
-        <v>506.20617525105831</v>
+        <v>511.57581480198968</v>
       </c>
       <c r="M3">
-        <v>515.09896417773246</v>
+        <v>520.96631623087603</v>
       </c>
       <c r="N3">
-        <v>540.93095124132526</v>
+        <v>546.82943164003632</v>
       </c>
       <c r="O3">
-        <v>565.99508010748116</v>
+        <v>574.12464002323202</v>
       </c>
       <c r="P3">
-        <v>587.13498282275748</v>
+        <v>595.14960268983464</v>
       </c>
       <c r="Q3">
-        <v>607.08339813700877</v>
+        <v>615.41748529926633</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -776,52 +747,52 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>488.11713123247631</v>
+        <v>487.29421051786909</v>
       </c>
       <c r="C4">
-        <v>535.24319496249575</v>
+        <v>534.91261391586409</v>
       </c>
       <c r="D4">
-        <v>478.2604392847191</v>
+        <v>478.59049052458482</v>
       </c>
       <c r="E4">
-        <v>471.2959219086535</v>
+        <v>471.30696692879002</v>
       </c>
       <c r="F4">
-        <v>472.58627509077257</v>
+        <v>473.80161551607699</v>
       </c>
       <c r="G4">
-        <v>465.89824092013208</v>
+        <v>464.99444656744078</v>
       </c>
       <c r="H4">
-        <v>454.78025987866641</v>
+        <v>454.19101569151462</v>
       </c>
       <c r="I4">
-        <v>442.51696645328241</v>
+        <v>442.57799016977413</v>
       </c>
       <c r="J4">
-        <v>453.05666046884932</v>
+        <v>452.82335212395873</v>
       </c>
       <c r="K4">
-        <v>464.15900994712968</v>
+        <v>464.65264268225349</v>
       </c>
       <c r="L4">
-        <v>493.88164821872209</v>
+        <v>496.11260705099039</v>
       </c>
       <c r="M4">
-        <v>502.38259001688061</v>
+        <v>502.95296199482408</v>
       </c>
       <c r="N4">
-        <v>487.6109732754926</v>
+        <v>489.36450890745351</v>
       </c>
       <c r="O4">
-        <v>484.66628050273857</v>
+        <v>487.24138002672947</v>
       </c>
       <c r="P4">
-        <v>490.20477459519537</v>
+        <v>491.52874005918522</v>
       </c>
       <c r="Q4">
-        <v>488.54653102198472</v>
+        <v>490.57504408130671</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -829,52 +800,52 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>472.41140856697172</v>
+        <v>469.54349993039</v>
       </c>
       <c r="C5">
-        <v>468.49976177948707</v>
+        <v>467.94206593355631</v>
       </c>
       <c r="D5">
-        <v>467.30175709167509</v>
+        <v>466.21227185475863</v>
       </c>
       <c r="E5">
-        <v>466.89450489850839</v>
+        <v>467.34690163140891</v>
       </c>
       <c r="F5">
-        <v>471.57231325195869</v>
+        <v>472.62105461120041</v>
       </c>
       <c r="G5">
-        <v>474.34908581389908</v>
+        <v>476.16535192310658</v>
       </c>
       <c r="H5">
-        <v>476.71347056632402</v>
+        <v>478.04377312373742</v>
       </c>
       <c r="I5">
-        <v>481.46795709622921</v>
+        <v>484.40051665622991</v>
       </c>
       <c r="J5">
-        <v>484.64873085662578</v>
+        <v>488.79606816901742</v>
       </c>
       <c r="K5">
-        <v>493.45880989951633</v>
+        <v>500.16140203963931</v>
       </c>
       <c r="L5">
-        <v>496.01602370967311</v>
+        <v>504.33593935735792</v>
       </c>
       <c r="M5">
-        <v>501.72191094026113</v>
+        <v>511.55479682190372</v>
       </c>
       <c r="N5">
-        <v>507.37512553473948</v>
+        <v>512.02808525271735</v>
       </c>
       <c r="O5">
-        <v>510.19060849578233</v>
+        <v>515.23058155325805</v>
       </c>
       <c r="P5">
-        <v>518.16076831008718</v>
+        <v>526.12250560397376</v>
       </c>
       <c r="Q5">
-        <v>511.36407945474281</v>
+        <v>518.8755629631213</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -882,52 +853,52 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>471.43226872935497</v>
+        <v>468.93032094338048</v>
       </c>
       <c r="C6">
-        <v>467.67206502118802</v>
+        <v>466.96146797294909</v>
       </c>
       <c r="D6">
-        <v>464.56911246059849</v>
+        <v>463.23784238715371</v>
       </c>
       <c r="E6">
-        <v>463.21540345568621</v>
+        <v>461.76814897974771</v>
       </c>
       <c r="F6">
-        <v>473.75397166061748</v>
+        <v>471.5261576758902</v>
       </c>
       <c r="G6">
-        <v>465.22599315238068</v>
+        <v>465.93202608254131</v>
       </c>
       <c r="H6">
-        <v>482.03793231857838</v>
+        <v>481.74101842090198</v>
       </c>
       <c r="I6">
-        <v>480.2371072550448</v>
+        <v>478.12438639003989</v>
       </c>
       <c r="J6">
-        <v>490.09608715433109</v>
+        <v>488.93410241738172</v>
       </c>
       <c r="K6">
-        <v>492.64061199298828</v>
+        <v>489.81822866615119</v>
       </c>
       <c r="L6">
-        <v>497.49455408975768</v>
+        <v>494.90925135542409</v>
       </c>
       <c r="M6">
-        <v>512.99839719608099</v>
+        <v>510.53053467646998</v>
       </c>
       <c r="N6">
-        <v>530.91273127601937</v>
+        <v>525.75285228270002</v>
       </c>
       <c r="O6">
-        <v>541.62484806562577</v>
+        <v>537.86155903760312</v>
       </c>
       <c r="P6">
-        <v>542.82147289007912</v>
+        <v>539.8871428420058</v>
       </c>
       <c r="Q6">
-        <v>525.58367914654843</v>
+        <v>524.16304064866733</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -935,52 +906,52 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>433.04415933614422</v>
+        <v>435.38716328164548</v>
       </c>
       <c r="C7">
-        <v>536.36040637481244</v>
+        <v>536.42775988060737</v>
       </c>
       <c r="D7">
-        <v>472.25553492269592</v>
+        <v>472.11261371088392</v>
       </c>
       <c r="E7">
-        <v>436.32431357274493</v>
+        <v>436.3323783437076</v>
       </c>
       <c r="F7">
-        <v>413.42830039192972</v>
+        <v>413.75658304068997</v>
       </c>
       <c r="G7">
-        <v>402.41599339925551</v>
+        <v>404.41015797630303</v>
       </c>
       <c r="H7">
-        <v>397.00700495393778</v>
+        <v>398.4507968084099</v>
       </c>
       <c r="I7">
-        <v>405.78938266528348</v>
+        <v>407.74026723211739</v>
       </c>
       <c r="J7">
-        <v>415.69898711482011</v>
+        <v>417.41989687560277</v>
       </c>
       <c r="K7">
-        <v>424.81889301247742</v>
+        <v>425.7372673403205</v>
       </c>
       <c r="L7">
-        <v>420.2905179934217</v>
+        <v>423.55332939991348</v>
       </c>
       <c r="M7">
-        <v>452.8999633242837</v>
+        <v>457.0335275748098</v>
       </c>
       <c r="N7">
-        <v>448.19378683881303</v>
+        <v>451.52141610610812</v>
       </c>
       <c r="O7">
-        <v>436.25584633794477</v>
+        <v>439.14568724142799</v>
       </c>
       <c r="P7">
-        <v>435.5213670029442</v>
+        <v>439.21237577727788</v>
       </c>
       <c r="Q7">
-        <v>437.12594497469792</v>
+        <v>441.15090370605668</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -988,52 +959,52 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>495.00335975985251</v>
+        <v>500.68286184544479</v>
       </c>
       <c r="C8">
-        <v>512.20097664146431</v>
+        <v>511.878657046998</v>
       </c>
       <c r="D8">
-        <v>481.54903752081032</v>
+        <v>481.04173206397451</v>
       </c>
       <c r="E8">
-        <v>460.71064810740842</v>
+        <v>462.3286354642666</v>
       </c>
       <c r="F8">
-        <v>451.89112525139791</v>
+        <v>454.21466400743151</v>
       </c>
       <c r="G8">
-        <v>449.45233306108292</v>
+        <v>451.26458745283992</v>
       </c>
       <c r="H8">
-        <v>451.87667051577421</v>
+        <v>455.07636453205907</v>
       </c>
       <c r="I8">
-        <v>447.60885259649223</v>
+        <v>450.94501928580848</v>
       </c>
       <c r="J8">
-        <v>440.83911995225651</v>
+        <v>444.71106996932031</v>
       </c>
       <c r="K8">
-        <v>472.57955435470859</v>
+        <v>476.13392587190481</v>
       </c>
       <c r="L8">
-        <v>488.54386790281058</v>
+        <v>495.82211953757081</v>
       </c>
       <c r="M8">
-        <v>486.43066058660258</v>
+        <v>494.0795760449891</v>
       </c>
       <c r="N8">
-        <v>480.60529091407761</v>
+        <v>486.00711339476601</v>
       </c>
       <c r="O8">
-        <v>467.24982057989212</v>
+        <v>472.88926406117571</v>
       </c>
       <c r="P8">
-        <v>475.19091621214449</v>
+        <v>481.62725631612358</v>
       </c>
       <c r="Q8">
-        <v>473.73850811910683</v>
+        <v>480.92324540911659</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1041,52 +1012,52 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>498.82324712450611</v>
+        <v>497.51230710727617</v>
       </c>
       <c r="C9">
-        <v>511.63690985406669</v>
+        <v>512.12050904836906</v>
       </c>
       <c r="D9">
-        <v>481.14758051590888</v>
+        <v>482.25235722182151</v>
       </c>
       <c r="E9">
-        <v>462.99491279270558</v>
+        <v>463.48465050820289</v>
       </c>
       <c r="F9">
-        <v>455.72933837242027</v>
+        <v>456.45285764071258</v>
       </c>
       <c r="G9">
-        <v>451.37306329929982</v>
+        <v>452.98304825713711</v>
       </c>
       <c r="H9">
-        <v>453.97684086238809</v>
+        <v>455.34365566071409</v>
       </c>
       <c r="I9">
-        <v>451.31092802997762</v>
+        <v>451.51252122426303</v>
       </c>
       <c r="J9">
-        <v>444.01678844407809</v>
+        <v>445.69998360630569</v>
       </c>
       <c r="K9">
-        <v>465.57553533969082</v>
+        <v>467.07814070711242</v>
       </c>
       <c r="L9">
-        <v>485.39318425637202</v>
+        <v>483.90827712461379</v>
       </c>
       <c r="M9">
-        <v>494.16666616543131</v>
+        <v>493.22922653866658</v>
       </c>
       <c r="N9">
-        <v>485.77862089785759</v>
+        <v>485.01938675868479</v>
       </c>
       <c r="O9">
-        <v>468.46182978090832</v>
+        <v>467.68045573769598</v>
       </c>
       <c r="P9">
-        <v>474.94922452917621</v>
+        <v>473.40930277924957</v>
       </c>
       <c r="Q9">
-        <v>478.53065582578603</v>
+        <v>478.18540954020631</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1094,52 +1065,52 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>506.77999103887379</v>
+        <v>496.08797092021769</v>
       </c>
       <c r="C10">
-        <v>512.11347414599618</v>
+        <v>511.83506971480227</v>
       </c>
       <c r="D10">
-        <v>480.96240893020132</v>
+        <v>480.95038146190473</v>
       </c>
       <c r="E10">
-        <v>462.78234370961582</v>
+        <v>459.85856613762752</v>
       </c>
       <c r="F10">
-        <v>454.57124812668911</v>
+        <v>451.93260296028251</v>
       </c>
       <c r="G10">
-        <v>453.08291654474061</v>
+        <v>449.69086457692129</v>
       </c>
       <c r="H10">
-        <v>455.60592648828089</v>
+        <v>452.47744969521841</v>
       </c>
       <c r="I10">
-        <v>451.69343381793112</v>
+        <v>448.66865383119142</v>
       </c>
       <c r="J10">
-        <v>444.1241356172207</v>
+        <v>440.86686082446778</v>
       </c>
       <c r="K10">
-        <v>465.75502110718207</v>
+        <v>461.28059878397289</v>
       </c>
       <c r="L10">
-        <v>483.46296252544198</v>
+        <v>477.17548082304029</v>
       </c>
       <c r="M10">
-        <v>492.18879195675788</v>
+        <v>488.62809740723168</v>
       </c>
       <c r="N10">
-        <v>484.24362910931552</v>
+        <v>480.66873762040302</v>
       </c>
       <c r="O10">
-        <v>465.77134277413802</v>
+        <v>463.94572011910839</v>
       </c>
       <c r="P10">
-        <v>468.39844947218432</v>
+        <v>466.78509452252939</v>
       </c>
       <c r="Q10">
-        <v>473.36121704376529</v>
+        <v>473.77451240295341</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -1147,52 +1118,52 @@
         <v>26</v>
       </c>
       <c r="B11">
-        <v>502.55885797989851</v>
+        <v>500.43258441927901</v>
       </c>
       <c r="C11">
-        <v>511.88298553524538</v>
+        <v>512.34039007145361</v>
       </c>
       <c r="D11">
-        <v>481.75473193623333</v>
+        <v>481.51576551307039</v>
       </c>
       <c r="E11">
-        <v>462.16252300024979</v>
+        <v>461.92726714387021</v>
       </c>
       <c r="F11">
-        <v>454.75343449477111</v>
+        <v>454.78152521889342</v>
       </c>
       <c r="G11">
-        <v>451.60753741297191</v>
+        <v>453.45662596087891</v>
       </c>
       <c r="H11">
-        <v>455.39152085933353</v>
+        <v>457.15376056170612</v>
       </c>
       <c r="I11">
-        <v>452.49760371704701</v>
+        <v>454.10344348977799</v>
       </c>
       <c r="J11">
-        <v>443.28336220460699</v>
+        <v>445.3393015864732</v>
       </c>
       <c r="K11">
-        <v>465.64663042576342</v>
+        <v>465.8978711841047</v>
       </c>
       <c r="L11">
-        <v>480.81362992387687</v>
+        <v>483.35055845426251</v>
       </c>
       <c r="M11">
-        <v>486.74901296753029</v>
+        <v>489.74587997395139</v>
       </c>
       <c r="N11">
-        <v>478.26832194901249</v>
+        <v>481.83761568974131</v>
       </c>
       <c r="O11">
-        <v>466.97381542463449</v>
+        <v>468.92590121808797</v>
       </c>
       <c r="P11">
-        <v>474.79369094606801</v>
+        <v>478.5532290056226</v>
       </c>
       <c r="Q11">
-        <v>465.71038963017401</v>
+        <v>469.08896617356572</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -1200,52 +1171,52 @@
         <v>27</v>
       </c>
       <c r="B12">
-        <v>466.7176756531868</v>
+        <v>466.0665148272368</v>
       </c>
       <c r="C12">
-        <v>463.20765903505929</v>
+        <v>464.21494373974713</v>
       </c>
       <c r="D12">
-        <v>459.65960114965748</v>
+        <v>460.85066048471242</v>
       </c>
       <c r="E12">
-        <v>458.30046949293632</v>
+        <v>459.24412827600878</v>
       </c>
       <c r="F12">
-        <v>457.97583763295029</v>
+        <v>459.93349276695437</v>
       </c>
       <c r="G12">
-        <v>454.26896537634673</v>
+        <v>455.56926236100799</v>
       </c>
       <c r="H12">
-        <v>454.07092140199268</v>
+        <v>454.50135848373378</v>
       </c>
       <c r="I12">
-        <v>455.80192727614218</v>
+        <v>454.94574491043448</v>
       </c>
       <c r="J12">
-        <v>461.08447410452032</v>
+        <v>458.79402729231953</v>
       </c>
       <c r="K12">
-        <v>465.71451605424193</v>
+        <v>464.7907242753293</v>
       </c>
       <c r="L12">
-        <v>473.48754378050819</v>
+        <v>472.77090196203068</v>
       </c>
       <c r="M12">
-        <v>488.53855541856029</v>
+        <v>484.4654059161507</v>
       </c>
       <c r="N12">
-        <v>498.6962851402721</v>
+        <v>496.86700769245363</v>
       </c>
       <c r="O12">
-        <v>503.17137096331368</v>
+        <v>498.54190370465659</v>
       </c>
       <c r="P12">
-        <v>511.18926012654401</v>
+        <v>508.82968611592241</v>
       </c>
       <c r="Q12">
-        <v>512.29678459888953</v>
+        <v>507.63613173215589</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1253,52 +1224,52 @@
         <v>28</v>
       </c>
       <c r="B13">
-        <v>465.96090761435818</v>
+        <v>464.79792227437412</v>
       </c>
       <c r="C13">
-        <v>464.03726568171408</v>
+        <v>464.47811087365483</v>
       </c>
       <c r="D13">
-        <v>453.52952404652018</v>
+        <v>454.7938175627537</v>
       </c>
       <c r="E13">
-        <v>448.10757641600873</v>
+        <v>450.50481810041379</v>
       </c>
       <c r="F13">
-        <v>446.5388183617107</v>
+        <v>448.82125161474443</v>
       </c>
       <c r="G13">
-        <v>452.49164781843979</v>
+        <v>453.48835596401591</v>
       </c>
       <c r="H13">
-        <v>457.11016401652358</v>
+        <v>459.03057118572389</v>
       </c>
       <c r="I13">
-        <v>459.76316944401088</v>
+        <v>461.28631525909952</v>
       </c>
       <c r="J13">
-        <v>469.2167148738219</v>
+        <v>470.93767009991029</v>
       </c>
       <c r="K13">
-        <v>474.54856737706871</v>
+        <v>477.14357962737972</v>
       </c>
       <c r="L13">
-        <v>486.92727881437548</v>
+        <v>489.1220510304758</v>
       </c>
       <c r="M13">
-        <v>491.31066132257348</v>
+        <v>493.90410325390121</v>
       </c>
       <c r="N13">
-        <v>494.29312761650078</v>
+        <v>497.38646573175731</v>
       </c>
       <c r="O13">
-        <v>499.21062809832819</v>
+        <v>503.34131085242359</v>
       </c>
       <c r="P13">
-        <v>507.52128529518012</v>
+        <v>510.47300327772939</v>
       </c>
       <c r="Q13">
-        <v>520.53204293109297</v>
+        <v>526.10575093329578</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1306,52 +1277,52 @@
         <v>29</v>
       </c>
       <c r="B14">
-        <v>435.15506047595233</v>
+        <v>436.50457018208948</v>
       </c>
       <c r="C14">
-        <v>535.48724632054439</v>
+        <v>535.1004677312302</v>
       </c>
       <c r="D14">
-        <v>471.20128374421199</v>
+        <v>470.97797952380472</v>
       </c>
       <c r="E14">
-        <v>436.4804581644363</v>
+        <v>434.90732072224279</v>
       </c>
       <c r="F14">
-        <v>413.48722756332052</v>
+        <v>411.83010243698641</v>
       </c>
       <c r="G14">
-        <v>403.91412953452561</v>
+        <v>401.77932815540271</v>
       </c>
       <c r="H14">
-        <v>399.06170303518059</v>
+        <v>398.63998650876852</v>
       </c>
       <c r="I14">
-        <v>407.58463254601543</v>
+        <v>404.52534655901701</v>
       </c>
       <c r="J14">
-        <v>414.6960959408454</v>
+        <v>414.2091241301016</v>
       </c>
       <c r="K14">
-        <v>423.89320726518542</v>
+        <v>423.7508820888936</v>
       </c>
       <c r="L14">
-        <v>425.22460838160492</v>
+        <v>426.63063689245621</v>
       </c>
       <c r="M14">
-        <v>462.75805225669723</v>
+        <v>463.20381300199608</v>
       </c>
       <c r="N14">
-        <v>466.18470509947463</v>
+        <v>465.41504197906738</v>
       </c>
       <c r="O14">
-        <v>452.5548502327876</v>
+        <v>453.29646201332201</v>
       </c>
       <c r="P14">
-        <v>448.35674597709709</v>
+        <v>446.9983543725121</v>
       </c>
       <c r="Q14">
-        <v>440.77751129609157</v>
+        <v>439.28781248532732</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1359,52 +1330,52 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>436.80781790960492</v>
+        <v>435.30842350872388</v>
       </c>
       <c r="C15">
-        <v>536.16068859858012</v>
+        <v>536.86664574287499</v>
       </c>
       <c r="D15">
-        <v>472.15292790987257</v>
+        <v>472.97058468915782</v>
       </c>
       <c r="E15">
-        <v>436.48335890714168</v>
+        <v>436.33893897463003</v>
       </c>
       <c r="F15">
-        <v>412.87348719095741</v>
+        <v>413.87851526499389</v>
       </c>
       <c r="G15">
-        <v>403.62257817867908</v>
+        <v>404.09124512882238</v>
       </c>
       <c r="H15">
-        <v>399.28075227090511</v>
+        <v>399.93682034033839</v>
       </c>
       <c r="I15">
-        <v>407.35307612160642</v>
+        <v>408.30850992111351</v>
       </c>
       <c r="J15">
-        <v>414.68476514589821</v>
+        <v>416.67068759196462</v>
       </c>
       <c r="K15">
-        <v>423.67366065882231</v>
+        <v>423.70797819777471</v>
       </c>
       <c r="L15">
-        <v>426.91787592448782</v>
+        <v>426.38136624917649</v>
       </c>
       <c r="M15">
-        <v>461.24662312097968</v>
+        <v>460.34191814747942</v>
       </c>
       <c r="N15">
-        <v>468.73097402414498</v>
+        <v>466.83378260998722</v>
       </c>
       <c r="O15">
-        <v>457.90527350881689</v>
+        <v>455.94448904828471</v>
       </c>
       <c r="P15">
-        <v>452.65670410356847</v>
+        <v>451.10151152964028</v>
       </c>
       <c r="Q15">
-        <v>443.33688304699342</v>
+        <v>442.50740547851052</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1412,52 +1383,52 @@
         <v>31</v>
       </c>
       <c r="B16">
-        <v>433.66122595804518</v>
+        <v>432.83482077468909</v>
       </c>
       <c r="C16">
-        <v>535.27592163366251</v>
+        <v>534.4808822587795</v>
       </c>
       <c r="D16">
-        <v>470.51796950395749</v>
+        <v>470.17664679531367</v>
       </c>
       <c r="E16">
-        <v>433.12626082221061</v>
+        <v>434.64200208637072</v>
       </c>
       <c r="F16">
-        <v>411.88149971737852</v>
+        <v>412.93863967837382</v>
       </c>
       <c r="G16">
-        <v>401.85548178199713</v>
+        <v>402.59193218759452</v>
       </c>
       <c r="H16">
-        <v>398.04263843942329</v>
+        <v>397.45514469446653</v>
       </c>
       <c r="I16">
-        <v>405.46193504704189</v>
+        <v>405.66690725715358</v>
       </c>
       <c r="J16">
-        <v>413.95943244606462</v>
+        <v>412.57925855426799</v>
       </c>
       <c r="K16">
-        <v>422.70749542061429</v>
+        <v>420.26013819429897</v>
       </c>
       <c r="L16">
-        <v>426.63341297336422</v>
+        <v>422.25359024177538</v>
       </c>
       <c r="M16">
-        <v>460.34673710484458</v>
+        <v>455.58057296757079</v>
       </c>
       <c r="N16">
-        <v>465.25854777360001</v>
+        <v>460.35630005097312</v>
       </c>
       <c r="O16">
-        <v>455.53714088281282</v>
+        <v>449.13938001434587</v>
       </c>
       <c r="P16">
-        <v>452.02277007020223</v>
+        <v>445.62318394656228</v>
       </c>
       <c r="Q16">
-        <v>444.64833038895199</v>
+        <v>437.92961973582129</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -1465,52 +1436,52 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>437.18713814822911</v>
+        <v>431.49721744561373</v>
       </c>
       <c r="C17">
-        <v>534.79546180867521</v>
+        <v>535.72798576574667</v>
       </c>
       <c r="D17">
-        <v>470.63391272423848</v>
+        <v>471.62998235712053</v>
       </c>
       <c r="E17">
-        <v>435.47595350728079</v>
+        <v>434.60245407278228</v>
       </c>
       <c r="F17">
-        <v>413.83513279179681</v>
+        <v>412.38584172219038</v>
       </c>
       <c r="G17">
-        <v>404.76738604859622</v>
+        <v>402.71996536078228</v>
       </c>
       <c r="H17">
-        <v>399.21419672313738</v>
+        <v>397.88372294657182</v>
       </c>
       <c r="I17">
-        <v>407.37929043338022</v>
+        <v>404.84351489300337</v>
       </c>
       <c r="J17">
-        <v>414.59268681884407</v>
+        <v>411.66230019730409</v>
       </c>
       <c r="K17">
-        <v>423.72134283517192</v>
+        <v>419.92005875091309</v>
       </c>
       <c r="L17">
-        <v>425.93247906830061</v>
+        <v>420.98393381348183</v>
       </c>
       <c r="M17">
-        <v>461.38197848376308</v>
+        <v>452.88556742007381</v>
       </c>
       <c r="N17">
-        <v>466.36736468233102</v>
+        <v>457.71014809877909</v>
       </c>
       <c r="O17">
-        <v>453.46701583436737</v>
+        <v>444.98765164592987</v>
       </c>
       <c r="P17">
-        <v>448.89737582210938</v>
+        <v>440.47301716694898</v>
       </c>
       <c r="Q17">
-        <v>439.63754941597881</v>
+        <v>432.83790146123789</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1518,52 +1489,52 @@
         <v>33</v>
       </c>
       <c r="B18">
-        <v>466.03574550723852</v>
+        <v>468.56683539956128</v>
       </c>
       <c r="C18">
-        <v>462.56971985112989</v>
+        <v>463.89457257977699</v>
       </c>
       <c r="D18">
-        <v>459.422650098453</v>
+        <v>461.02004302389702</v>
       </c>
       <c r="E18">
-        <v>457.8940561369547</v>
+        <v>462.20844623973471</v>
       </c>
       <c r="F18">
-        <v>457.35929364148973</v>
+        <v>462.254308450579</v>
       </c>
       <c r="G18">
-        <v>447.57788142639691</v>
+        <v>451.84864351018291</v>
       </c>
       <c r="H18">
-        <v>455.39577188727731</v>
+        <v>459.09358874451061</v>
       </c>
       <c r="I18">
-        <v>449.91344380864979</v>
+        <v>455.10654569007528</v>
       </c>
       <c r="J18">
-        <v>451.91034911300369</v>
+        <v>454.40113710673171</v>
       </c>
       <c r="K18">
-        <v>451.36441332715532</v>
+        <v>454.02581339133519</v>
       </c>
       <c r="L18">
-        <v>450.59049154924548</v>
+        <v>453.51867925571901</v>
       </c>
       <c r="M18">
-        <v>452.08384880102392</v>
+        <v>452.73306439175838</v>
       </c>
       <c r="N18">
-        <v>456.69095796360318</v>
+        <v>458.56382159345043</v>
       </c>
       <c r="O18">
-        <v>457.92852940904771</v>
+        <v>460.08531725457738</v>
       </c>
       <c r="P18">
-        <v>469.08050024089999</v>
+        <v>469.80106542311552</v>
       </c>
       <c r="Q18">
-        <v>466.92257006035368</v>
+        <v>465.00436795256633</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1571,52 +1542,52 @@
         <v>34</v>
       </c>
       <c r="B19">
-        <v>466.24789024125317</v>
+        <v>467.18844369378718</v>
       </c>
       <c r="C19">
-        <v>462.02765878481358</v>
+        <v>461.95601063464829</v>
       </c>
       <c r="D19">
-        <v>457.01987000543159</v>
+        <v>456.80103595467722</v>
       </c>
       <c r="E19">
-        <v>454.82856868129318</v>
+        <v>453.81438895694629</v>
       </c>
       <c r="F19">
-        <v>462.32681771201783</v>
+        <v>460.64106918578932</v>
       </c>
       <c r="G19">
-        <v>451.88153012602839</v>
+        <v>452.42918281881367</v>
       </c>
       <c r="H19">
-        <v>455.74997843193262</v>
+        <v>455.45409171410319</v>
       </c>
       <c r="I19">
-        <v>450.26541396347022</v>
+        <v>450.43653142461852</v>
       </c>
       <c r="J19">
-        <v>450.78260881523369</v>
+        <v>453.46371874163941</v>
       </c>
       <c r="K19">
-        <v>451.20957753584997</v>
+        <v>453.01366579114813</v>
       </c>
       <c r="L19">
-        <v>443.88574934940448</v>
+        <v>446.17605201200348</v>
       </c>
       <c r="M19">
-        <v>456.81207100366908</v>
+        <v>458.76210730594403</v>
       </c>
       <c r="N19">
-        <v>464.78110978769638</v>
+        <v>465.61998416301788</v>
       </c>
       <c r="O19">
-        <v>465.97801664914681</v>
+        <v>467.03632625313088</v>
       </c>
       <c r="P19">
-        <v>469.76445098573129</v>
+        <v>470.27571007791869</v>
       </c>
       <c r="Q19">
-        <v>465.10634853284438</v>
+        <v>464.95486087657338</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1624,52 +1595,52 @@
         <v>35</v>
       </c>
       <c r="B20">
-        <v>466.8310761529234</v>
+        <v>467.37476933451421</v>
       </c>
       <c r="C20">
-        <v>461.30575911846131</v>
+        <v>461.71566659483102</v>
       </c>
       <c r="D20">
-        <v>455.73398490624038</v>
+        <v>455.64997346547602</v>
       </c>
       <c r="E20">
-        <v>449.71683054112111</v>
+        <v>448.0646119495604</v>
       </c>
       <c r="F20">
-        <v>459.57889466031531</v>
+        <v>459.82566515389072</v>
       </c>
       <c r="G20">
-        <v>458.59644551363328</v>
+        <v>459.73226302040757</v>
       </c>
       <c r="H20">
-        <v>448.64434959925688</v>
+        <v>451.24498829902001</v>
       </c>
       <c r="I20">
-        <v>438.35908251294381</v>
+        <v>438.38899642015889</v>
       </c>
       <c r="J20">
-        <v>447.33750319969369</v>
+        <v>448.41081252578869</v>
       </c>
       <c r="K20">
-        <v>444.2391714827283</v>
+        <v>444.61183245734611</v>
       </c>
       <c r="L20">
-        <v>445.06784449655652</v>
+        <v>445.27296319319299</v>
       </c>
       <c r="M20">
-        <v>453.08927061204753</v>
+        <v>452.41402802259569</v>
       </c>
       <c r="N20">
-        <v>464.99448720015022</v>
+        <v>464.0138994992289</v>
       </c>
       <c r="O20">
-        <v>469.07349145448899</v>
+        <v>465.40331416481001</v>
       </c>
       <c r="P20">
-        <v>457.29698387314579</v>
+        <v>451.60028821174262</v>
       </c>
       <c r="Q20">
-        <v>456.09362716709683</v>
+        <v>451.59788424098917</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -1677,52 +1648,52 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>474.70112871705282</v>
+        <v>473.14205429726189</v>
       </c>
       <c r="C21">
-        <v>509.30535127829052</v>
+        <v>508.62252728577442</v>
       </c>
       <c r="D21">
-        <v>464.82800979524762</v>
+        <v>464.52182146172612</v>
       </c>
       <c r="E21">
-        <v>460.97432918499288</v>
+        <v>459.6688935697947</v>
       </c>
       <c r="F21">
-        <v>454.07708264508028</v>
+        <v>453.01964445194949</v>
       </c>
       <c r="G21">
-        <v>460.3027906228341</v>
+        <v>457.08390043449799</v>
       </c>
       <c r="H21">
-        <v>466.76751301564678</v>
+        <v>461.52342589132189</v>
       </c>
       <c r="I21">
-        <v>497.24179126183373</v>
+        <v>490.34712356466503</v>
       </c>
       <c r="J21">
-        <v>505.44582686764562</v>
+        <v>497.89260846917023</v>
       </c>
       <c r="K21">
-        <v>506.45396254597932</v>
+        <v>500.80113218968188</v>
       </c>
       <c r="L21">
-        <v>516.68523529492347</v>
+        <v>510.43717155408581</v>
       </c>
       <c r="M21">
-        <v>531.0652948331126</v>
+        <v>525.42481351137042</v>
       </c>
       <c r="N21">
-        <v>546.32807544477623</v>
+        <v>540.31038125592113</v>
       </c>
       <c r="O21">
-        <v>564.3160408061932</v>
+        <v>559.71864762980044</v>
       </c>
       <c r="P21">
-        <v>587.95000922227769</v>
+        <v>585.15707878054718</v>
       </c>
       <c r="Q21">
-        <v>614.11120794937926</v>
+        <v>611.06655250936535</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1730,52 +1701,52 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>478.10584645253448</v>
+        <v>473.73069670114182</v>
       </c>
       <c r="C22">
-        <v>509.95401172341792</v>
+        <v>509.42805406559461</v>
       </c>
       <c r="D22">
-        <v>465.40807727603402</v>
+        <v>464.74004294753951</v>
       </c>
       <c r="E22">
-        <v>460.66833402088059</v>
+        <v>460.52345902404238</v>
       </c>
       <c r="F22">
-        <v>453.82036518131878</v>
+        <v>455.74226508763462</v>
       </c>
       <c r="G22">
-        <v>457.12980053914441</v>
+        <v>459.78482484620929</v>
       </c>
       <c r="H22">
-        <v>455.81180483602571</v>
+        <v>458.43282182051081</v>
       </c>
       <c r="I22">
-        <v>487.33818819745312</v>
+        <v>490.34895877900641</v>
       </c>
       <c r="J22">
-        <v>501.19898038267411</v>
+        <v>503.45515064400769</v>
       </c>
       <c r="K22">
-        <v>500.02348116489691</v>
+        <v>504.65674554545109</v>
       </c>
       <c r="L22">
-        <v>507.91283468800532</v>
+        <v>511.75375564338049</v>
       </c>
       <c r="M22">
-        <v>524.03795319695848</v>
+        <v>527.91129915612726</v>
       </c>
       <c r="N22">
-        <v>539.68946914133403</v>
+        <v>542.83824524155727</v>
       </c>
       <c r="O22">
-        <v>555.37407179234515</v>
+        <v>560.76584495071768</v>
       </c>
       <c r="P22">
-        <v>580.13421423438115</v>
+        <v>586.96964146397738</v>
       </c>
       <c r="Q22">
-        <v>599.74466742994821</v>
+        <v>608.23229312793001</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -1783,52 +1754,52 @@
         <v>38</v>
       </c>
       <c r="B23">
-        <v>464.27659003427158</v>
+        <v>465.68489508706239</v>
       </c>
       <c r="C23">
-        <v>463.90964515911128</v>
+        <v>465.31466487857062</v>
       </c>
       <c r="D23">
-        <v>478.80396644041599</v>
+        <v>482.28365390251412</v>
       </c>
       <c r="E23">
-        <v>465.37197584246411</v>
+        <v>467.54359137245888</v>
       </c>
       <c r="F23">
-        <v>459.13965815874559</v>
+        <v>459.55496591468449</v>
       </c>
       <c r="G23">
-        <v>477.97296949286851</v>
+        <v>479.75726113385872</v>
       </c>
       <c r="H23">
-        <v>502.84161233561713</v>
+        <v>502.25828312334181</v>
       </c>
       <c r="I23">
-        <v>531.74263829691847</v>
+        <v>533.16821625900911</v>
       </c>
       <c r="J23">
-        <v>538.75147129579454</v>
+        <v>538.00937425099403</v>
       </c>
       <c r="K23">
-        <v>558.96428312418652</v>
+        <v>558.11264453012586</v>
       </c>
       <c r="L23">
-        <v>571.11299176979378</v>
+        <v>571.94671293864269</v>
       </c>
       <c r="M23">
-        <v>586.37500591287051</v>
+        <v>588.62600697837922</v>
       </c>
       <c r="N23">
-        <v>593.46667858802334</v>
+        <v>595.38242244202991</v>
       </c>
       <c r="O23">
-        <v>610.08585998523358</v>
+        <v>613.65847947098143</v>
       </c>
       <c r="P23">
-        <v>628.48569735055412</v>
+        <v>631.02843280522461</v>
       </c>
       <c r="Q23">
-        <v>648.89330022940464</v>
+        <v>651.88256156458408</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -1836,52 +1807,52 @@
         <v>39</v>
       </c>
       <c r="B24">
-        <v>640.68393300497166</v>
+        <v>641.03112189132821</v>
       </c>
       <c r="C24">
-        <v>640.68393300497166</v>
+        <v>641.03112189132821</v>
       </c>
       <c r="D24">
-        <v>666.34388896214989</v>
+        <v>664.60678386882876</v>
       </c>
       <c r="E24">
-        <v>657.84049500188132</v>
+        <v>658.10322895829472</v>
       </c>
       <c r="F24">
-        <v>692.32439648946331</v>
+        <v>695.53919196981997</v>
       </c>
       <c r="G24">
-        <v>781.70922370314634</v>
+        <v>781.67735907646966</v>
       </c>
       <c r="H24">
-        <v>749.47305665227339</v>
+        <v>748.48342758387048</v>
       </c>
       <c r="I24">
-        <v>769.53316557277719</v>
+        <v>768.21324376973689</v>
       </c>
       <c r="J24">
-        <v>787.19214167465736</v>
+        <v>784.41559042767756</v>
       </c>
       <c r="K24">
-        <v>805.35006014448913</v>
+        <v>796.948396552536</v>
       </c>
       <c r="L24">
-        <v>820.29791924254334</v>
+        <v>814.56850254736605</v>
       </c>
       <c r="M24">
-        <v>836.76798375829708</v>
+        <v>830.76305360876665</v>
       </c>
       <c r="N24">
-        <v>836.36587679653451</v>
+        <v>831.447087289514</v>
       </c>
       <c r="O24">
-        <v>834.97403891585395</v>
+        <v>828.17328902387715</v>
       </c>
       <c r="P24">
-        <v>841.63234619088928</v>
+        <v>836.75652442945375</v>
       </c>
       <c r="Q24">
-        <v>848.04832548081447</v>
+        <v>841.84694317261983</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1889,52 +1860,52 @@
         <v>40</v>
       </c>
       <c r="B25">
-        <v>648.48371569951507</v>
+        <v>648.32600220972859</v>
       </c>
       <c r="C25">
-        <v>648.48371569951507</v>
+        <v>648.32600220972859</v>
       </c>
       <c r="D25">
-        <v>667.84779169743399</v>
+        <v>665.24361505869308</v>
       </c>
       <c r="E25">
-        <v>682.82033943356771</v>
+        <v>679.95629211148503</v>
       </c>
       <c r="F25">
-        <v>715.93969171476965</v>
+        <v>711.796850862317</v>
       </c>
       <c r="G25">
-        <v>738.4440128515763</v>
+        <v>736.78732210021747</v>
       </c>
       <c r="H25">
-        <v>782.69354152338974</v>
+        <v>781.01599697978338</v>
       </c>
       <c r="I25">
-        <v>817.49466090921806</v>
+        <v>812.90087483286788</v>
       </c>
       <c r="J25">
-        <v>841.16217140673541</v>
+        <v>835.59572262257586</v>
       </c>
       <c r="K25">
-        <v>845.982828446643</v>
+        <v>838.6020409492611</v>
       </c>
       <c r="L25">
-        <v>844.86488615950213</v>
+        <v>836.88671296832013</v>
       </c>
       <c r="M25">
-        <v>866.49368334761198</v>
+        <v>861.81240237265399</v>
       </c>
       <c r="N25">
-        <v>888.17499416046553</v>
+        <v>886.81635896928708</v>
       </c>
       <c r="O25">
-        <v>907.66199219907992</v>
+        <v>907.89734071404905</v>
       </c>
       <c r="P25">
-        <v>912.44142571519581</v>
+        <v>911.28581322431592</v>
       </c>
       <c r="Q25">
-        <v>917.38818466075372</v>
+        <v>915.23697543243247</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1942,52 +1913,52 @@
         <v>41</v>
       </c>
       <c r="B26">
-        <v>645.9704694756955</v>
+        <v>645.73047409516084</v>
       </c>
       <c r="C26">
-        <v>645.9704694756955</v>
+        <v>643.98854763401187</v>
       </c>
       <c r="D26">
-        <v>659.42102315687464</v>
+        <v>655.15746626808129</v>
       </c>
       <c r="E26">
-        <v>660.42600494196154</v>
+        <v>658.24066129660787</v>
       </c>
       <c r="F26">
-        <v>693.51331483706304</v>
+        <v>689.48962111344269</v>
       </c>
       <c r="G26">
-        <v>716.83820937055145</v>
+        <v>717.33730773246918</v>
       </c>
       <c r="H26">
-        <v>723.07550747279106</v>
+        <v>724.58645745207605</v>
       </c>
       <c r="I26">
-        <v>744.2695247713591</v>
+        <v>743.4132303588824</v>
       </c>
       <c r="J26">
-        <v>736.82182677651213</v>
+        <v>732.84032989797004</v>
       </c>
       <c r="K26">
-        <v>720.9727291169911</v>
+        <v>716.46749441160819</v>
       </c>
       <c r="L26">
-        <v>703.14001146581688</v>
+        <v>700.50582738783737</v>
       </c>
       <c r="M26">
-        <v>754.5841642491971</v>
+        <v>749.47849671917606</v>
       </c>
       <c r="N26">
-        <v>799.29727632471713</v>
+        <v>798.19422232772342</v>
       </c>
       <c r="O26">
-        <v>785.48632646169074</v>
+        <v>783.30135729081132</v>
       </c>
       <c r="P26">
-        <v>791.48106058013002</v>
+        <v>793.03130662868557</v>
       </c>
       <c r="Q26">
-        <v>795.96759495050946</v>
+        <v>798.38412076166912</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -1995,52 +1966,52 @@
         <v>42</v>
       </c>
       <c r="B27">
-        <v>650.62260633404696</v>
+        <v>652.04715593512765</v>
       </c>
       <c r="C27">
-        <v>650.12912728679385</v>
+        <v>650.55420311333853</v>
       </c>
       <c r="D27">
-        <v>659.53500892375666</v>
+        <v>659.09816174066998</v>
       </c>
       <c r="E27">
-        <v>700.52601495735803</v>
+        <v>698.33873641640253</v>
       </c>
       <c r="F27">
-        <v>683.99712197155804</v>
+        <v>684.34761508158954</v>
       </c>
       <c r="G27">
-        <v>720.2214350356345</v>
+        <v>719.28454748202716</v>
       </c>
       <c r="H27">
-        <v>711.22542480407913</v>
+        <v>713.59676121795189</v>
       </c>
       <c r="I27">
-        <v>688.48164295283414</v>
+        <v>690.19974738012547</v>
       </c>
       <c r="J27">
-        <v>687.24835526929371</v>
+        <v>688.35853920050317</v>
       </c>
       <c r="K27">
-        <v>712.92719241372629</v>
+        <v>712.62416444612109</v>
       </c>
       <c r="L27">
-        <v>739.33029121473646</v>
+        <v>739.45946358213871</v>
       </c>
       <c r="M27">
-        <v>759.17276998907676</v>
+        <v>758.97156570297307</v>
       </c>
       <c r="N27">
-        <v>782.35369927998238</v>
+        <v>776.36975005317549</v>
       </c>
       <c r="O27">
-        <v>760.5919864488319</v>
+        <v>755.52120397308317</v>
       </c>
       <c r="P27">
-        <v>788.09714611710319</v>
+        <v>783.84126824343798</v>
       </c>
       <c r="Q27">
-        <v>798.94471213996064</v>
+        <v>794.85180955868748</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -2048,52 +2019,52 @@
         <v>43</v>
       </c>
       <c r="B28">
-        <v>418.94972515323133</v>
+        <v>417.11391842192182</v>
       </c>
       <c r="C28">
-        <v>453.82635423277549</v>
-      </c>
-      <c r="D28">
-        <v>420.60926315512847</v>
+        <v>454.35288355295393</v>
+      </c>
+      <c r="D28" s="2">
+        <v>420.99140365287172</v>
       </c>
       <c r="E28">
-        <v>400.65459028309618</v>
+        <v>401.92555041048257</v>
       </c>
       <c r="F28">
-        <v>387.21217506411642</v>
+        <v>387.64020479773671</v>
       </c>
       <c r="G28">
-        <v>403.48325580900001</v>
+        <v>404.08484638341417</v>
       </c>
       <c r="H28">
-        <v>411.73537310846632</v>
+        <v>410.5478758523484</v>
       </c>
       <c r="I28">
-        <v>410.73151649993667</v>
+        <v>412.10844827858051</v>
       </c>
       <c r="J28">
-        <v>423.12921384465608</v>
+        <v>420.20648358030962</v>
       </c>
       <c r="K28">
-        <v>402.07901444354991</v>
+        <v>401.39998441856608</v>
       </c>
       <c r="L28">
-        <v>392.70326217907052</v>
+        <v>390.40248765360838</v>
       </c>
       <c r="M28">
-        <v>409.89558580045099</v>
+        <v>409.57802287526471</v>
       </c>
       <c r="N28">
-        <v>419.0202545807515</v>
+        <v>420.44442167836252</v>
       </c>
       <c r="O28">
-        <v>436.27023988345769</v>
+        <v>437.11018015020232</v>
       </c>
       <c r="P28">
-        <v>447.32497230953157</v>
+        <v>447.80218695655071</v>
       </c>
       <c r="Q28">
-        <v>469.70177594377469</v>
+        <v>468.12334705852481</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -2101,52 +2072,52 @@
         <v>44</v>
       </c>
       <c r="B29">
-        <v>388.88415993178842</v>
+        <v>392.64152691392371</v>
       </c>
       <c r="C29">
-        <v>453.55730923331993</v>
+        <v>454.95535593410392</v>
       </c>
       <c r="D29">
-        <v>418.43350968309443</v>
-      </c>
-      <c r="E29">
-        <v>393.4965815564326</v>
-      </c>
-      <c r="F29">
-        <v>373.80488528943408</v>
+        <v>420.19287174017228</v>
+      </c>
+      <c r="E29" s="2">
+        <v>394.31005875946522</v>
+      </c>
+      <c r="F29" s="2">
+        <v>375.13347614594642</v>
       </c>
       <c r="G29">
-        <v>379.7033047344683</v>
+        <v>379.38327894928449</v>
       </c>
       <c r="H29">
-        <v>370.86734962670192</v>
+        <v>371.92026150756459</v>
       </c>
       <c r="I29">
-        <v>375.03201980285382</v>
+        <v>375.43731480938391</v>
       </c>
       <c r="J29">
-        <v>380.73499414183777</v>
-      </c>
-      <c r="K29" s="2">
-        <v>359.0302710532589</v>
+        <v>381.18784686272232</v>
+      </c>
+      <c r="K29">
+        <v>358.74505907393183</v>
       </c>
       <c r="L29">
-        <v>359.52016343012389</v>
+        <v>359.68802183094698</v>
       </c>
       <c r="M29">
-        <v>358.03069216364048</v>
+        <v>359.22399587432483</v>
       </c>
       <c r="N29">
-        <v>365.2872524270108</v>
+        <v>367.71339024073461</v>
       </c>
       <c r="O29">
-        <v>375.86303228065259</v>
+        <v>377.93262150881208</v>
       </c>
       <c r="P29">
-        <v>389.38733071923889</v>
+        <v>391.99526198909768</v>
       </c>
       <c r="Q29">
-        <v>407.55847664368952</v>
+        <v>410.6608464986212</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -2154,52 +2125,52 @@
         <v>45</v>
       </c>
       <c r="B30">
-        <v>427.91797390185201</v>
+        <v>432.18454082566558</v>
       </c>
       <c r="C30">
-        <v>447.04605819410432</v>
-      </c>
-      <c r="D30">
-        <v>428.82221989507087</v>
-      </c>
-      <c r="E30">
-        <v>407.9202407977341</v>
+        <v>446.93096253180971</v>
+      </c>
+      <c r="D30" s="2">
+        <v>429.23865621410181</v>
+      </c>
+      <c r="E30" s="2">
+        <v>408.28030355533889</v>
       </c>
       <c r="F30">
-        <v>393.53337872947668</v>
+        <v>393.42998991632368</v>
       </c>
       <c r="G30">
-        <v>405.18495835703402</v>
+        <v>403.51711295608112</v>
       </c>
       <c r="H30">
-        <v>393.35083996296993</v>
+        <v>392.7838116315591</v>
       </c>
       <c r="I30">
-        <v>400.12278850160948</v>
+        <v>398.75831986732379</v>
       </c>
       <c r="J30">
-        <v>398.7837145454659</v>
+        <v>402.34265304072551</v>
       </c>
       <c r="K30">
-        <v>398.19653493692948</v>
+        <v>398.89443386060992</v>
       </c>
       <c r="L30">
-        <v>388.1756333221781</v>
+        <v>387.20621324811071</v>
       </c>
       <c r="M30">
-        <v>391.71142416799648</v>
+        <v>392.70070625451359</v>
       </c>
       <c r="N30">
-        <v>393.80920488676702</v>
+        <v>394.36026737601202</v>
       </c>
       <c r="O30">
-        <v>405.27767643608257</v>
+        <v>407.95353179285001</v>
       </c>
       <c r="P30">
-        <v>423.52699164164397</v>
+        <v>425.78793830611568</v>
       </c>
       <c r="Q30">
-        <v>442.1433391986651</v>
+        <v>445.34831190669541</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -2207,52 +2178,52 @@
         <v>46</v>
       </c>
       <c r="B31">
-        <v>439.97638273497938</v>
+        <v>439.916660716016</v>
       </c>
       <c r="C31">
-        <v>445.62462739821041</v>
+        <v>446.25685332989639</v>
       </c>
       <c r="D31">
-        <v>427.41145811795542</v>
-      </c>
-      <c r="E31">
-        <v>406.05310153895431</v>
+        <v>428.00431090256188</v>
+      </c>
+      <c r="E31" s="2">
+        <v>406.20413507774492</v>
       </c>
       <c r="F31">
-        <v>391.98426616869102</v>
+        <v>392.43886234259043</v>
       </c>
       <c r="G31">
-        <v>402.7898790670481</v>
+        <v>402.44525219678462</v>
       </c>
       <c r="H31">
-        <v>393.18794542998211</v>
+        <v>392.81899896058758</v>
       </c>
       <c r="I31">
-        <v>399.11111333738012</v>
+        <v>397.64879425958168</v>
       </c>
       <c r="J31">
-        <v>401.98001989543712</v>
+        <v>401.40185051799631</v>
       </c>
       <c r="K31">
-        <v>405.70432615078289</v>
+        <v>405.58369953967588</v>
       </c>
       <c r="L31">
-        <v>403.08453299109209</v>
+        <v>402.98959613552142</v>
       </c>
       <c r="M31">
-        <v>403.88192631176622</v>
+        <v>404.33361285308757</v>
       </c>
       <c r="N31">
-        <v>403.50465042433461</v>
+        <v>402.60185465000473</v>
       </c>
       <c r="O31">
-        <v>409.85269978295958</v>
+        <v>407.22462201324697</v>
       </c>
       <c r="P31">
-        <v>420.86678012905651</v>
+        <v>418.67945079117442</v>
       </c>
       <c r="Q31">
-        <v>416.41330677136062</v>
+        <v>413.91236261113642</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -2260,52 +2231,52 @@
         <v>47</v>
       </c>
       <c r="B32">
-        <v>399.45121144357302</v>
+        <v>400.96716378854728</v>
       </c>
       <c r="C32">
-        <v>454.21898694703378</v>
+        <v>454.58745341455511</v>
       </c>
       <c r="D32">
-        <v>418.98948014608533</v>
-      </c>
-      <c r="E32">
-        <v>394.96726921152401</v>
+        <v>419.76765223013939</v>
+      </c>
+      <c r="E32" s="2">
+        <v>395.05065535540871</v>
       </c>
       <c r="F32">
-        <v>375.97336097256942</v>
+        <v>375.59849894971939</v>
       </c>
       <c r="G32">
-        <v>381.4749515734037</v>
+        <v>382.05596819475647</v>
       </c>
       <c r="H32">
-        <v>375.5363823566513</v>
+        <v>376.15980353830628</v>
       </c>
       <c r="I32">
-        <v>379.32863350342649</v>
+        <v>378.97671604167971</v>
       </c>
       <c r="J32">
-        <v>391.35781769341821</v>
+        <v>393.24910618321371</v>
       </c>
       <c r="K32">
-        <v>373.86812275422028</v>
+        <v>376.34964332668687</v>
       </c>
       <c r="L32">
-        <v>370.66309922447249</v>
+        <v>373.49721999711488</v>
       </c>
       <c r="M32">
-        <v>364.93893544170732</v>
+        <v>368.80976573715418</v>
       </c>
       <c r="N32">
-        <v>368.07481536273917</v>
+        <v>372.14807004136122</v>
       </c>
       <c r="O32">
-        <v>376.58269803272549</v>
+        <v>381.45759133285941</v>
       </c>
       <c r="P32">
-        <v>382.62049538655168</v>
+        <v>387.98914195321157</v>
       </c>
       <c r="Q32">
-        <v>402.20334908426128</v>
+        <v>408.82717930769928</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -2313,52 +2284,52 @@
         <v>48</v>
       </c>
       <c r="B33">
-        <v>400.7880377315488</v>
+        <v>395.2317956453316</v>
       </c>
       <c r="C33">
-        <v>455.46780956937278</v>
+        <v>454.35479705344562</v>
       </c>
       <c r="D33">
-        <v>420.68253865079032</v>
-      </c>
-      <c r="E33">
-        <v>395.38700973295272</v>
+        <v>419.47919136551212</v>
+      </c>
+      <c r="E33" s="2">
+        <v>394.17865294622499</v>
       </c>
       <c r="F33">
-        <v>376.29275552573938</v>
+        <v>375.22510966290889</v>
       </c>
       <c r="G33">
-        <v>380.14264049845337</v>
+        <v>380.93202094270038</v>
       </c>
       <c r="H33">
-        <v>374.33734355673829</v>
+        <v>375.64683849178778</v>
       </c>
       <c r="I33">
-        <v>376.68280547032259</v>
+        <v>378.52390682896032</v>
       </c>
       <c r="J33">
-        <v>388.96903156102758</v>
+        <v>392.29462071897279</v>
       </c>
       <c r="K33">
-        <v>371.8610890628637</v>
+        <v>371.49872813614769</v>
       </c>
       <c r="L33">
-        <v>369.55766876704308</v>
+        <v>371.18959147725133</v>
       </c>
       <c r="M33">
-        <v>365.37136453074561</v>
+        <v>365.10163733436212</v>
       </c>
       <c r="N33">
-        <v>368.98858893695711</v>
+        <v>370.11140564103079</v>
       </c>
       <c r="O33">
-        <v>377.76727816673002</v>
+        <v>379.0878622537503</v>
       </c>
       <c r="P33">
-        <v>386.97951442584491</v>
+        <v>388.39386737731752</v>
       </c>
       <c r="Q33">
-        <v>410.72976823557849</v>
+        <v>409.6554470329728</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -2366,52 +2337,52 @@
         <v>49</v>
       </c>
       <c r="B34">
-        <v>400.76862213503131</v>
+        <v>399.56188354455992</v>
       </c>
       <c r="C34">
-        <v>454.45115951815887</v>
+        <v>454.58485216278427</v>
       </c>
       <c r="D34">
-        <v>419.32194000263308</v>
-      </c>
-      <c r="E34">
-        <v>394.35009477152522</v>
+        <v>419.65948253775872</v>
+      </c>
+      <c r="E34" s="2">
+        <v>394.47140508604411</v>
       </c>
       <c r="F34">
-        <v>375.20891081552878</v>
+        <v>375.39589999821999</v>
       </c>
       <c r="G34">
-        <v>380.63917715823811</v>
+        <v>381.14983193607162</v>
       </c>
       <c r="H34">
-        <v>375.10117840920998</v>
+        <v>373.99400724046859</v>
       </c>
       <c r="I34">
-        <v>378.60323812364959</v>
+        <v>377.72907897455912</v>
       </c>
       <c r="J34">
-        <v>393.66890423365612</v>
+        <v>391.46347876150361</v>
       </c>
       <c r="K34">
-        <v>373.66914748588061</v>
+        <v>374.12215368890031</v>
       </c>
       <c r="L34">
-        <v>370.93378601544481</v>
+        <v>369.42594932350818</v>
       </c>
       <c r="M34">
-        <v>364.67800083453739</v>
+        <v>363.07040291816998</v>
       </c>
       <c r="N34">
-        <v>369.33634926960713</v>
+        <v>367.69626117142531</v>
       </c>
       <c r="O34">
-        <v>378.3668503961394</v>
+        <v>378.35058988064412</v>
       </c>
       <c r="P34">
-        <v>384.30557384133391</v>
+        <v>384.4350769952344</v>
       </c>
       <c r="Q34">
-        <v>405.67709572796008</v>
+        <v>407.15350976276818</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -2419,52 +2390,52 @@
         <v>50</v>
       </c>
       <c r="B35">
-        <v>398.95902948907218</v>
+        <v>397.68640790429811</v>
       </c>
       <c r="C35">
-        <v>455.26818944491208</v>
+        <v>454.59434071009929</v>
       </c>
       <c r="D35">
-        <v>420.07840199938101</v>
-      </c>
-      <c r="E35">
-        <v>395.28286571707503</v>
-      </c>
-      <c r="F35">
-        <v>375.24123063121522</v>
+        <v>419.62153585690658</v>
+      </c>
+      <c r="E35" s="2">
+        <v>395.03957505258319</v>
+      </c>
+      <c r="F35" s="2">
+        <v>375.1517488806968</v>
       </c>
       <c r="G35">
-        <v>379.91080728034228</v>
+        <v>380.00952750318038</v>
       </c>
       <c r="H35">
-        <v>374.63217329429199</v>
+        <v>374.05625889170011</v>
       </c>
       <c r="I35">
-        <v>378.48532317475042</v>
+        <v>377.62989135615959</v>
       </c>
       <c r="J35">
-        <v>392.36501752544751</v>
+        <v>391.69791718197553</v>
       </c>
       <c r="K35">
-        <v>373.20374297943238</v>
+        <v>372.65789633518432</v>
       </c>
       <c r="L35">
-        <v>370.84636138961918</v>
+        <v>370.45804011447359</v>
       </c>
       <c r="M35">
-        <v>362.90952177777137</v>
+        <v>363.70642690143961</v>
       </c>
       <c r="N35">
-        <v>367.60225974167918</v>
+        <v>367.54184103892698</v>
       </c>
       <c r="O35">
-        <v>375.40264656103528</v>
+        <v>375.96170479818818</v>
       </c>
       <c r="P35">
-        <v>378.82389978259488</v>
+        <v>382.98624340090589</v>
       </c>
       <c r="Q35">
-        <v>398.15362363011309</v>
+        <v>403.99498407472072</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -2472,52 +2443,52 @@
         <v>51</v>
       </c>
       <c r="B36">
-        <v>399.49874736507422</v>
+        <v>402.3839255260354</v>
       </c>
       <c r="C36">
-        <v>454.41741640906912</v>
+        <v>454.71252475133662</v>
       </c>
       <c r="D36">
-        <v>419.34977460503097</v>
-      </c>
-      <c r="E36">
-        <v>393.68663681452648</v>
+        <v>419.17164315317848</v>
+      </c>
+      <c r="E36" s="2">
+        <v>394.35852015337139</v>
       </c>
       <c r="F36">
-        <v>374.71113576416963</v>
+        <v>375.30829370213308</v>
       </c>
       <c r="G36">
-        <v>380.63581213766469</v>
+        <v>379.28691771260452</v>
       </c>
       <c r="H36">
-        <v>373.48451658420868</v>
+        <v>373.42622212672501</v>
       </c>
       <c r="I36">
-        <v>378.76108218585728</v>
+        <v>377.11912975201687</v>
       </c>
       <c r="J36">
-        <v>390.47162002709001</v>
+        <v>387.85956149756419</v>
       </c>
       <c r="K36">
-        <v>373.24822143613773</v>
+        <v>371.07371942416182</v>
       </c>
       <c r="L36">
-        <v>371.61738538328552</v>
+        <v>370.95934979059581</v>
       </c>
       <c r="M36">
-        <v>369.87157910527651</v>
+        <v>369.2405289496171</v>
       </c>
       <c r="N36">
-        <v>375.31562980021732</v>
+        <v>372.86659007285368</v>
       </c>
       <c r="O36">
-        <v>382.83150048560913</v>
+        <v>382.96395524886208</v>
       </c>
       <c r="P36">
-        <v>387.7319855493343</v>
+        <v>386.54807242743948</v>
       </c>
       <c r="Q36">
-        <v>406.60717801697331</v>
+        <v>405.94535585206989</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -2525,52 +2496,52 @@
         <v>52</v>
       </c>
       <c r="B37">
-        <v>402.22726887356163</v>
+        <v>399.00778191868289</v>
       </c>
       <c r="C37">
-        <v>456.07777710474443</v>
+        <v>455.19891906727759</v>
       </c>
       <c r="D37">
-        <v>420.68828727541859</v>
-      </c>
-      <c r="E37">
-        <v>395.80413816488999</v>
+        <v>420.25003534426253</v>
+      </c>
+      <c r="E37" s="2">
+        <v>394.18728491304972</v>
       </c>
       <c r="F37">
-        <v>376.43760183373342</v>
+        <v>374.82250010017589</v>
       </c>
       <c r="G37">
-        <v>382.28852435746109</v>
+        <v>380.15029800757827</v>
       </c>
       <c r="H37">
-        <v>376.67595754091502</v>
+        <v>373.99300327912408</v>
       </c>
       <c r="I37">
-        <v>380.32937057284607</v>
+        <v>376.54126070597238</v>
       </c>
       <c r="J37">
-        <v>391.21605293997641</v>
+        <v>390.1510981893565</v>
       </c>
       <c r="K37">
-        <v>373.61027327897011</v>
+        <v>372.60549989595722</v>
       </c>
       <c r="L37">
-        <v>374.33331993633749</v>
+        <v>372.53663381943198</v>
       </c>
       <c r="M37">
-        <v>370.42590406524459</v>
+        <v>369.32097065219972</v>
       </c>
       <c r="N37">
-        <v>374.68554859988961</v>
+        <v>374.04049737948162</v>
       </c>
       <c r="O37">
-        <v>381.80909820959522</v>
+        <v>384.15910538359577</v>
       </c>
       <c r="P37">
-        <v>386.75887507364041</v>
+        <v>390.66834341013691</v>
       </c>
       <c r="Q37">
-        <v>407.52832188547529</v>
+        <v>410.06779303581709</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -2578,52 +2549,52 @@
         <v>53</v>
       </c>
       <c r="B38">
-        <v>398.74166469704119</v>
+        <v>400.31872936395678</v>
       </c>
       <c r="C38">
-        <v>454.580701956616</v>
+        <v>454.50168822595958</v>
       </c>
       <c r="D38">
-        <v>419.53165468756561</v>
-      </c>
-      <c r="E38">
-        <v>394.03725737232861</v>
+        <v>419.0940750608948</v>
+      </c>
+      <c r="E38" s="2">
+        <v>394.2483261761808</v>
       </c>
       <c r="F38">
-        <v>374.60757860916141</v>
+        <v>374.93181851121528</v>
       </c>
       <c r="G38">
-        <v>379.59765709627538</v>
+        <v>380.93826752299088</v>
       </c>
       <c r="H38">
-        <v>372.7911136981146</v>
+        <v>374.59310266236838</v>
       </c>
       <c r="I38">
-        <v>377.70527308983242</v>
+        <v>378.18287782757949</v>
       </c>
       <c r="J38">
-        <v>387.33311961805589</v>
+        <v>389.04785260037983</v>
       </c>
       <c r="K38">
-        <v>371.95158139837469</v>
+        <v>372.57701678108668</v>
       </c>
       <c r="L38">
-        <v>368.78319803507861</v>
+        <v>371.8902413018626</v>
       </c>
       <c r="M38">
-        <v>367.67491822173832</v>
+        <v>368.75985454649788</v>
       </c>
       <c r="N38">
-        <v>369.84920600044882</v>
+        <v>371.07742567717492</v>
       </c>
       <c r="O38">
-        <v>378.03030193967618</v>
+        <v>379.93458143302678</v>
       </c>
       <c r="P38">
-        <v>384.52613597623792</v>
+        <v>384.91451752343698</v>
       </c>
       <c r="Q38">
-        <v>406.15151334814487</v>
+        <v>410.61190907525997</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -2631,52 +2602,52 @@
         <v>54</v>
       </c>
       <c r="B39">
-        <v>400.42476473937398</v>
+        <v>398.20276602278261</v>
       </c>
       <c r="C39">
-        <v>455.10580878910213</v>
+        <v>454.22150630178078</v>
       </c>
       <c r="D39">
-        <v>420.37549482581738</v>
-      </c>
-      <c r="E39">
-        <v>395.96934522048241</v>
+        <v>419.33818798743528</v>
+      </c>
+      <c r="E39" s="2">
+        <v>393.30670056955842</v>
       </c>
       <c r="F39">
-        <v>375.76070889599958</v>
+        <v>374.06415592560103</v>
       </c>
       <c r="G39">
-        <v>381.58023737695879</v>
+        <v>379.4616167728621</v>
       </c>
       <c r="H39">
-        <v>375.89234072007201</v>
+        <v>372.52244149791449</v>
       </c>
       <c r="I39">
-        <v>378.98579840885111</v>
+        <v>377.7609621507105</v>
       </c>
       <c r="J39">
-        <v>392.05376794126681</v>
+        <v>390.09279067745263</v>
       </c>
       <c r="K39">
-        <v>374.71992503175608</v>
+        <v>371.9524733686053</v>
       </c>
       <c r="L39">
-        <v>371.71259161941822</v>
+        <v>370.83685830157748</v>
       </c>
       <c r="M39">
-        <v>368.43652997000498</v>
+        <v>368.12884488852961</v>
       </c>
       <c r="N39">
-        <v>371.5696823644418</v>
+        <v>371.68719568306551</v>
       </c>
       <c r="O39">
-        <v>380.08719656980111</v>
+        <v>378.39680373614237</v>
       </c>
       <c r="P39">
-        <v>383.12879474948193</v>
+        <v>386.27425117468721</v>
       </c>
       <c r="Q39">
-        <v>404.64559505136577</v>
+        <v>409.3113403436015</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -2684,52 +2655,52 @@
         <v>55</v>
       </c>
       <c r="B40">
-        <v>396.84711412296701</v>
+        <v>399.24886028642891</v>
       </c>
       <c r="C40">
-        <v>455.25356658101163</v>
+        <v>454.21027395778401</v>
       </c>
       <c r="D40">
-        <v>419.51201712701311</v>
-      </c>
-      <c r="E40">
-        <v>393.93006215271618</v>
+        <v>419.32857559512053</v>
+      </c>
+      <c r="E40" s="2">
+        <v>395.26394255904722</v>
       </c>
       <c r="F40">
-        <v>374.39206207024102</v>
+        <v>375.81182708855567</v>
       </c>
       <c r="G40">
-        <v>378.78243047453782</v>
+        <v>381.66523885652771</v>
       </c>
       <c r="H40">
-        <v>373.38418272633942</v>
+        <v>376.13114751191023</v>
       </c>
       <c r="I40">
-        <v>377.45475969492219</v>
+        <v>379.89923135596871</v>
       </c>
       <c r="J40">
-        <v>389.46709556139598</v>
+        <v>394.68767060835279</v>
       </c>
       <c r="K40">
-        <v>371.08200596195411</v>
+        <v>375.03020441587108</v>
       </c>
       <c r="L40">
-        <v>370.65580271697792</v>
+        <v>372.83409769225841</v>
       </c>
       <c r="M40">
-        <v>363.47712637356437</v>
+        <v>365.17486437139081</v>
       </c>
       <c r="N40">
-        <v>367.8595170924674</v>
+        <v>369.8596923196846</v>
       </c>
       <c r="O40">
-        <v>375.82968235579472</v>
+        <v>377.5640543624736</v>
       </c>
       <c r="P40">
-        <v>380.57297165619951</v>
+        <v>381.32464388476723</v>
       </c>
       <c r="Q40">
-        <v>404.78240401525721</v>
+        <v>404.3354456482208</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -2737,52 +2708,52 @@
         <v>56</v>
       </c>
       <c r="B41">
-        <v>417.44538510811151</v>
+        <v>410.64034591029201</v>
       </c>
       <c r="C41">
-        <v>445.40313232793369</v>
-      </c>
-      <c r="D41">
-        <v>413.99188873327319</v>
+        <v>445.48078443916842</v>
+      </c>
+      <c r="D41" s="2">
+        <v>412.17703083713388</v>
       </c>
       <c r="E41">
-        <v>382.61573474960858</v>
+        <v>380.33324512804609</v>
       </c>
       <c r="F41">
-        <v>387.74212968403077</v>
+        <v>385.34733810404191</v>
       </c>
       <c r="G41">
-        <v>407.18149013929218</v>
+        <v>404.14102112601739</v>
       </c>
       <c r="H41">
-        <v>439.56915402981599</v>
+        <v>434.42363683147659</v>
       </c>
       <c r="I41">
-        <v>435.79353792089711</v>
+        <v>429.59463016949712</v>
       </c>
       <c r="J41">
-        <v>443.34276160953198</v>
+        <v>438.73747686885793</v>
       </c>
       <c r="K41">
-        <v>451.73252283240367</v>
+        <v>446.97082133911198</v>
       </c>
       <c r="L41">
-        <v>449.21535968139699</v>
+        <v>446.02983708934738</v>
       </c>
       <c r="M41">
-        <v>460.88303485949012</v>
+        <v>456.04917025324988</v>
       </c>
       <c r="N41">
-        <v>459.83693290260578</v>
+        <v>455.83015360207412</v>
       </c>
       <c r="O41">
-        <v>467.8492105632933</v>
+        <v>463.62202703772022</v>
       </c>
       <c r="P41">
-        <v>476.12557469393312</v>
+        <v>472.62406966754889</v>
       </c>
       <c r="Q41">
-        <v>480.17131188741467</v>
+        <v>477.90609021557867</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -2790,52 +2761,52 @@
         <v>57</v>
       </c>
       <c r="B42">
-        <v>403.53740061304671</v>
+        <v>406.1679049970457</v>
       </c>
       <c r="C42">
-        <v>444.52740072953918</v>
-      </c>
-      <c r="D42">
-        <v>406.53077540442638</v>
+        <v>444.64061176740648</v>
+      </c>
+      <c r="D42" s="2">
+        <v>409.45951801527099</v>
       </c>
       <c r="E42">
-        <v>376.58835361683089</v>
+        <v>379.06297919261578</v>
       </c>
       <c r="F42">
-        <v>379.87715820006349</v>
+        <v>383.09856341390048</v>
       </c>
       <c r="G42">
-        <v>401.73632376809468</v>
+        <v>404.16862474044149</v>
       </c>
       <c r="H42">
-        <v>426.68159523113673</v>
+        <v>429.94763074388311</v>
       </c>
       <c r="I42">
-        <v>413.18957649077117</v>
+        <v>413.60739943607763</v>
       </c>
       <c r="J42">
-        <v>416.0932916491505</v>
+        <v>417.88845741479298</v>
       </c>
       <c r="K42">
-        <v>407.37004367158562</v>
+        <v>408.37000474280973</v>
       </c>
       <c r="L42">
-        <v>394.83038097370229</v>
+        <v>393.56869946661908</v>
       </c>
       <c r="M42">
-        <v>399.40683423366733</v>
+        <v>399.66650289919733</v>
       </c>
       <c r="N42">
-        <v>406.06624824995117</v>
+        <v>405.29334202231797</v>
       </c>
       <c r="O42">
-        <v>405.81909297242998</v>
+        <v>404.14657165947301</v>
       </c>
       <c r="P42">
-        <v>415.97180747919418</v>
+        <v>413.48971557894208</v>
       </c>
       <c r="Q42">
-        <v>435.03390913306163</v>
+        <v>433.45423685341763</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -2843,52 +2814,52 @@
         <v>58</v>
       </c>
       <c r="B43">
-        <v>407.94541359700281</v>
+        <v>410.67760978145338</v>
       </c>
       <c r="C43">
-        <v>443.67136014998829</v>
-      </c>
-      <c r="D43">
-        <v>408.44457436050948</v>
+        <v>444.86080127593209</v>
+      </c>
+      <c r="D43" s="2">
+        <v>410.99214054279349</v>
       </c>
       <c r="E43">
-        <v>377.51486435353382</v>
+        <v>379.96177276325199</v>
       </c>
       <c r="F43">
-        <v>382.03952236558848</v>
+        <v>384.68990425721501</v>
       </c>
       <c r="G43">
-        <v>402.320895825793</v>
+        <v>403.58546885841611</v>
       </c>
       <c r="H43">
-        <v>426.59318982315727</v>
+        <v>430.91747489320483</v>
       </c>
       <c r="I43">
-        <v>410.75008170571027</v>
+        <v>414.257997987355</v>
       </c>
       <c r="J43">
-        <v>413.87209846254422</v>
+        <v>418.28507624133221</v>
       </c>
       <c r="K43">
-        <v>408.8882400041835</v>
+        <v>412.9001965991128</v>
       </c>
       <c r="L43">
-        <v>402.81218741160382</v>
+        <v>405.45194033439611</v>
       </c>
       <c r="M43">
-        <v>406.81199939528477</v>
+        <v>408.12062578845428</v>
       </c>
       <c r="N43">
-        <v>410.7116713902671</v>
+        <v>413.20241956457431</v>
       </c>
       <c r="O43">
-        <v>406.78179657620348</v>
+        <v>409.13214702605922</v>
       </c>
       <c r="P43">
-        <v>410.29614611188327</v>
+        <v>411.76176174928548</v>
       </c>
       <c r="Q43">
-        <v>423.73129882620441</v>
+        <v>426.38803270555781</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -2896,52 +2867,52 @@
         <v>59</v>
       </c>
       <c r="B44">
-        <v>463.45983028773293</v>
+        <v>463.46715188845332</v>
       </c>
       <c r="C44">
-        <v>464.05248008791568</v>
+        <v>463.80548848667922</v>
       </c>
       <c r="D44">
-        <v>470.50841249689279</v>
+        <v>470.74499584956561</v>
       </c>
       <c r="E44">
-        <v>442.56112962549838</v>
+        <v>442.83497473136691</v>
       </c>
       <c r="F44">
-        <v>417.75474058488419</v>
+        <v>416.48481114095961</v>
       </c>
       <c r="G44">
-        <v>416.34064835583217</v>
+        <v>413.17237812019829</v>
       </c>
       <c r="H44">
-        <v>414.87654454067263</v>
+        <v>410.7426834744175</v>
       </c>
       <c r="I44">
-        <v>423.70607525134898</v>
+        <v>420.95332192925059</v>
       </c>
       <c r="J44">
-        <v>426.65549827129388</v>
+        <v>423.23330168276249</v>
       </c>
       <c r="K44">
-        <v>431.03884945324103</v>
+        <v>428.30766239180258</v>
       </c>
       <c r="L44">
-        <v>447.40224352132401</v>
+        <v>445.10778523212929</v>
       </c>
       <c r="M44">
-        <v>465.14314244655111</v>
+        <v>463.00242597367861</v>
       </c>
       <c r="N44">
-        <v>479.40713850512492</v>
+        <v>477.02942120033242</v>
       </c>
       <c r="O44">
-        <v>492.08784486354938</v>
+        <v>490.04302862188518</v>
       </c>
       <c r="P44">
-        <v>505.37901146362049</v>
+        <v>503.39207913609209</v>
       </c>
       <c r="Q44">
-        <v>526.14727436500971</v>
+        <v>525.25073346355816</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -2949,52 +2920,52 @@
         <v>60</v>
       </c>
       <c r="B45">
-        <v>469.50529754557709</v>
+        <v>468.93876854000399</v>
       </c>
       <c r="C45">
-        <v>469.31309156461339</v>
+        <v>468.59645538857518</v>
       </c>
       <c r="D45">
-        <v>449.96829161708092</v>
+        <v>449.9227824182866</v>
       </c>
       <c r="E45">
-        <v>458.08859495063922</v>
+        <v>457.85977503827849</v>
       </c>
       <c r="F45">
-        <v>473.10187887201539</v>
+        <v>472.8570451339699</v>
       </c>
       <c r="G45">
-        <v>494.78490340563411</v>
+        <v>492.94506753389783</v>
       </c>
       <c r="H45">
-        <v>507.39746435772253</v>
+        <v>501.49663313299101</v>
       </c>
       <c r="I45">
-        <v>503.78839162190337</v>
+        <v>498.12589153693722</v>
       </c>
       <c r="J45">
-        <v>499.21995429334271</v>
+        <v>496.08882229858301</v>
       </c>
       <c r="K45">
-        <v>504.10325378626783</v>
+        <v>501.08322116908658</v>
       </c>
       <c r="L45">
-        <v>535.77192847224887</v>
+        <v>532.41872370492354</v>
       </c>
       <c r="M45">
-        <v>558.33091240128124</v>
+        <v>557.47821229954843</v>
       </c>
       <c r="N45">
-        <v>569.22623665792287</v>
+        <v>569.03109468187313</v>
       </c>
       <c r="O45">
-        <v>589.14376469201909</v>
+        <v>590.74444588482504</v>
       </c>
       <c r="P45">
-        <v>598.32151373869237</v>
+        <v>600.74219225880381</v>
       </c>
       <c r="Q45">
-        <v>589.36704524020968</v>
+        <v>593.09332947535813</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -3002,52 +2973,52 @@
         <v>61</v>
       </c>
       <c r="B46">
-        <v>469.6210754163007</v>
+        <v>470.76397499456039</v>
       </c>
       <c r="C46">
-        <v>511.23999531453251</v>
+        <v>510.77204900724769</v>
       </c>
       <c r="D46">
-        <v>459.60957239673411</v>
+        <v>459.08478619628971</v>
       </c>
       <c r="E46">
-        <v>463.48748263391019</v>
+        <v>459.85389327329159</v>
       </c>
       <c r="F46">
-        <v>461.01573846486087</v>
+        <v>459.23642880620042</v>
       </c>
       <c r="G46">
-        <v>491.4150896022627</v>
+        <v>486.59666603464302</v>
       </c>
       <c r="H46">
-        <v>484.18041753998671</v>
+        <v>480.4126550252987</v>
       </c>
       <c r="I46">
-        <v>482.86716280312578</v>
+        <v>479.96355206845652</v>
       </c>
       <c r="J46">
-        <v>505.18748073318619</v>
+        <v>499.96665811496081</v>
       </c>
       <c r="K46">
-        <v>538.2523640981932</v>
+        <v>531.15892528753341</v>
       </c>
       <c r="L46">
-        <v>567.84013763463929</v>
+        <v>559.92979199445949</v>
       </c>
       <c r="M46">
-        <v>574.05904344919929</v>
+        <v>568.38749401146242</v>
       </c>
       <c r="N46">
-        <v>577.47693377456756</v>
+        <v>570.78806169793449</v>
       </c>
       <c r="O46">
-        <v>587.72771719903301</v>
+        <v>580.56818993312868</v>
       </c>
       <c r="P46">
-        <v>593.23034520717704</v>
+        <v>586.38418027889247</v>
       </c>
       <c r="Q46">
-        <v>592.67175560340593</v>
+        <v>584.66958737257744</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -3055,57 +3026,57 @@
         <v>62</v>
       </c>
       <c r="B47">
-        <v>460.95281052065468</v>
+        <v>462.75667467908181</v>
       </c>
       <c r="C47">
-        <v>457.63418633882299</v>
+        <v>459.03580488704449</v>
       </c>
       <c r="D47">
-        <v>461.61949691301697</v>
+        <v>464.29733502152249</v>
       </c>
       <c r="E47">
-        <v>466.17873649440833</v>
+        <v>470.65305989125272</v>
       </c>
       <c r="F47">
-        <v>475.95873750052402</v>
+        <v>481.95701314095811</v>
       </c>
       <c r="G47">
-        <v>510.08242294134141</v>
+        <v>515.37992495893002</v>
       </c>
       <c r="H47">
-        <v>496.40199804995098</v>
+        <v>503.65729134361288</v>
       </c>
       <c r="I47">
-        <v>490.31798199464589</v>
+        <v>493.10908325468358</v>
       </c>
       <c r="J47">
-        <v>479.51535568553942</v>
+        <v>485.60560385237142</v>
       </c>
       <c r="K47">
-        <v>506.99483947009708</v>
+        <v>514.22805259889185</v>
       </c>
       <c r="L47">
-        <v>505.13026553209818</v>
+        <v>513.5440070835798</v>
       </c>
       <c r="M47">
-        <v>520.15867686728791</v>
+        <v>528.83881326224889</v>
       </c>
       <c r="N47">
-        <v>526.55534310207668</v>
+        <v>536.03185799833693</v>
       </c>
       <c r="O47">
-        <v>525.14906775205623</v>
+        <v>532.67344251559973</v>
       </c>
       <c r="P47">
-        <v>524.79108200006851</v>
+        <v>531.85564760336922</v>
       </c>
       <c r="Q47">
-        <v>525.38895189700668</v>
+        <v>532.04610080570251</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:Q28 B30:Q47 B29:L29 N29:Q29">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="C2:Q47">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3115,7 +3086,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.trans.carotenes.natif/Resultats_total.trans.carotenes.natif_moy_RMSEP.xlsx
@@ -1,220 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\total.trans.carotenes.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -247,50 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -332,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -399,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -575,2518 +350,2539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="17" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>460.77347334420813</v>
+        <v>460.299099160638</v>
       </c>
       <c r="C2">
-        <v>543.84610505803425</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D2">
-        <v>471.78719021186203</v>
+        <v>542.7619194745687</v>
       </c>
       <c r="E2">
-        <v>454.54624682009592</v>
+        <v>470.5397596539024</v>
       </c>
       <c r="F2">
-        <v>433.44880101827192</v>
+        <v>453.5389164412828</v>
       </c>
       <c r="G2">
-        <v>428.46666602838491</v>
+        <v>432.7049729610485</v>
       </c>
       <c r="H2">
-        <v>415.33408947654141</v>
+        <v>426.6889121716056</v>
       </c>
       <c r="I2">
-        <v>411.34693653213321</v>
+        <v>412.9010338321326</v>
       </c>
       <c r="J2">
-        <v>417.472216221304</v>
+        <v>409.1369658042127</v>
       </c>
       <c r="K2">
-        <v>430.8956080698357</v>
+        <v>415.2270601936721</v>
       </c>
       <c r="L2">
-        <v>445.65025982064941</v>
+        <v>428.3020542227877</v>
       </c>
       <c r="M2">
-        <v>441.31009544138681</v>
+        <v>443.4460515307445</v>
       </c>
       <c r="N2">
-        <v>461.13927668141088</v>
+        <v>440.9492529353201</v>
       </c>
       <c r="O2">
-        <v>473.97910630958302</v>
+        <v>459.2388823364272</v>
       </c>
       <c r="P2">
-        <v>474.07314912121592</v>
+        <v>472.248394701794</v>
       </c>
       <c r="Q2">
-        <v>465.38693200551501</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>470.5726902723396</v>
+      </c>
+      <c r="R2">
+        <v>462.4128426236115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>479.79797402406712</v>
+        <v>482.2014180455205</v>
       </c>
       <c r="C3">
-        <v>509.06114048037398</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D3">
-        <v>463.49719915012668</v>
+        <v>510.2997169895491</v>
       </c>
       <c r="E3">
-        <v>460.37040616812408</v>
+        <v>465.3522395442595</v>
       </c>
       <c r="F3">
-        <v>460.5634245246095</v>
+        <v>462.8747926021714</v>
       </c>
       <c r="G3">
-        <v>471.18548967130431</v>
+        <v>462.959762943742</v>
       </c>
       <c r="H3">
-        <v>473.83833353427349</v>
+        <v>472.762918178418</v>
       </c>
       <c r="I3">
-        <v>498.37147808557899</v>
+        <v>475.6235472021424</v>
       </c>
       <c r="J3">
-        <v>505.44823206382148</v>
+        <v>498.3833031498048</v>
       </c>
       <c r="K3">
-        <v>513.82086534592679</v>
+        <v>505.1264984548403</v>
       </c>
       <c r="L3">
-        <v>511.57581480198968</v>
+        <v>513.3718026500528</v>
       </c>
       <c r="M3">
-        <v>520.96631623087603</v>
+        <v>510.0090470449492</v>
       </c>
       <c r="N3">
-        <v>546.82943164003632</v>
+        <v>519.6177463835116</v>
       </c>
       <c r="O3">
-        <v>574.12464002323202</v>
+        <v>545.3353536982097</v>
       </c>
       <c r="P3">
-        <v>595.14960268983464</v>
+        <v>571.3792531294064</v>
       </c>
       <c r="Q3">
-        <v>615.41748529926633</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>591.924385244514</v>
+      </c>
+      <c r="R3">
+        <v>610.2475916896819</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>487.29421051786909</v>
+        <v>486.5595730494504</v>
       </c>
       <c r="C4">
-        <v>534.91261391586409</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D4">
-        <v>478.59049052458482</v>
+        <v>534.9728293146042</v>
       </c>
       <c r="E4">
-        <v>471.30696692879002</v>
+        <v>478.534268978038</v>
       </c>
       <c r="F4">
-        <v>473.80161551607699</v>
+        <v>471.3264692064396</v>
       </c>
       <c r="G4">
-        <v>464.99444656744078</v>
+        <v>475.5079350549697</v>
       </c>
       <c r="H4">
-        <v>454.19101569151462</v>
+        <v>466.557873043569</v>
       </c>
       <c r="I4">
-        <v>442.57799016977413</v>
+        <v>456.1445962364624</v>
       </c>
       <c r="J4">
-        <v>452.82335212395873</v>
+        <v>441.484640909556</v>
       </c>
       <c r="K4">
-        <v>464.65264268225349</v>
+        <v>452.9084470141728</v>
       </c>
       <c r="L4">
-        <v>496.11260705099039</v>
+        <v>463.8338234524896</v>
       </c>
       <c r="M4">
-        <v>502.95296199482408</v>
+        <v>494.5154832116511</v>
       </c>
       <c r="N4">
-        <v>489.36450890745351</v>
+        <v>502.8240804436481</v>
       </c>
       <c r="O4">
-        <v>487.24138002672947</v>
+        <v>488.0894745434143</v>
       </c>
       <c r="P4">
-        <v>491.52874005918522</v>
+        <v>483.7564224463292</v>
       </c>
       <c r="Q4">
-        <v>490.57504408130671</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>488.6459663110888</v>
+      </c>
+      <c r="R4">
+        <v>485.7796975182416</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>469.54349993039</v>
+        <v>470.5314444911998</v>
       </c>
       <c r="C5">
-        <v>467.94206593355631</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D5">
-        <v>466.21227185475863</v>
+        <v>468.2055879207503</v>
       </c>
       <c r="E5">
-        <v>467.34690163140891</v>
+        <v>466.9189993549606</v>
       </c>
       <c r="F5">
-        <v>472.62105461120041</v>
+        <v>467.9823608154018</v>
       </c>
       <c r="G5">
-        <v>476.16535192310658</v>
+        <v>471.3304128211435</v>
       </c>
       <c r="H5">
-        <v>478.04377312373742</v>
+        <v>474.6644644479709</v>
       </c>
       <c r="I5">
-        <v>484.40051665622991</v>
+        <v>477.9362731755596</v>
       </c>
       <c r="J5">
-        <v>488.79606816901742</v>
+        <v>483.8363541321255</v>
       </c>
       <c r="K5">
-        <v>500.16140203963931</v>
+        <v>486.2001878196688</v>
       </c>
       <c r="L5">
-        <v>504.33593935735792</v>
+        <v>494.6732811769911</v>
       </c>
       <c r="M5">
-        <v>511.55479682190372</v>
+        <v>497.8485433165801</v>
       </c>
       <c r="N5">
-        <v>512.02808525271735</v>
+        <v>505.2232680786715</v>
       </c>
       <c r="O5">
-        <v>515.23058155325805</v>
+        <v>508.9760178474537</v>
       </c>
       <c r="P5">
-        <v>526.12250560397376</v>
+        <v>511.2340051114302</v>
       </c>
       <c r="Q5">
-        <v>518.8755629631213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>521.3747037939197</v>
+      </c>
+      <c r="R5">
+        <v>513.4441462494656</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>468.93032094338048</v>
+        <v>470.1154423862649</v>
       </c>
       <c r="C6">
-        <v>466.96146797294909</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D6">
-        <v>463.23784238715371</v>
+        <v>467.4462574609727</v>
       </c>
       <c r="E6">
-        <v>461.76814897974771</v>
+        <v>464.5336086294565</v>
       </c>
       <c r="F6">
-        <v>471.5261576758902</v>
+        <v>463.9547123290357</v>
       </c>
       <c r="G6">
-        <v>465.93202608254131</v>
+        <v>475.4995830682705</v>
       </c>
       <c r="H6">
-        <v>481.74101842090198</v>
+        <v>468.4410899119587</v>
       </c>
       <c r="I6">
-        <v>478.12438639003989</v>
+        <v>487.3530548438181</v>
       </c>
       <c r="J6">
-        <v>488.93410241738172</v>
+        <v>485.2720070956852</v>
       </c>
       <c r="K6">
-        <v>489.81822866615119</v>
+        <v>494.4459583397773</v>
       </c>
       <c r="L6">
-        <v>494.90925135542409</v>
+        <v>494.9306492120836</v>
       </c>
       <c r="M6">
-        <v>510.53053467646998</v>
+        <v>501.0537611065283</v>
       </c>
       <c r="N6">
-        <v>525.75285228270002</v>
+        <v>516.6357777254025</v>
       </c>
       <c r="O6">
-        <v>537.86155903760312</v>
+        <v>532.0313872046058</v>
       </c>
       <c r="P6">
-        <v>539.8871428420058</v>
+        <v>544.2157395597425</v>
       </c>
       <c r="Q6">
-        <v>524.16304064866733</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>545.508292035359</v>
+      </c>
+      <c r="R6">
+        <v>529.2600831987759</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>435.38716328164548</v>
+        <v>432.0563148988435</v>
       </c>
       <c r="C7">
-        <v>536.42775988060737</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D7">
-        <v>472.11261371088392</v>
+        <v>536.1170917395139</v>
       </c>
       <c r="E7">
-        <v>436.3323783437076</v>
+        <v>471.5060203759131</v>
       </c>
       <c r="F7">
-        <v>413.75658304068997</v>
+        <v>435.3884135059841</v>
       </c>
       <c r="G7">
-        <v>404.41015797630303</v>
+        <v>412.5447065739039</v>
       </c>
       <c r="H7">
-        <v>398.4507968084099</v>
+        <v>402.5324562382976</v>
       </c>
       <c r="I7">
-        <v>407.74026723211739</v>
+        <v>397.0402968849488</v>
       </c>
       <c r="J7">
-        <v>417.41989687560277</v>
+        <v>406.047724099332</v>
       </c>
       <c r="K7">
-        <v>425.7372673403205</v>
+        <v>415.4346595577778</v>
       </c>
       <c r="L7">
-        <v>423.55332939991348</v>
+        <v>423.4891038208698</v>
       </c>
       <c r="M7">
-        <v>457.0335275748098</v>
+        <v>423.3956126373558</v>
       </c>
       <c r="N7">
-        <v>451.52141610610812</v>
+        <v>455.0503327512663</v>
       </c>
       <c r="O7">
-        <v>439.14568724142799</v>
+        <v>450.7657837168165</v>
       </c>
       <c r="P7">
-        <v>439.21237577727788</v>
+        <v>436.437979466102</v>
       </c>
       <c r="Q7">
-        <v>441.15090370605668</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>437.1500344762036</v>
+      </c>
+      <c r="R7">
+        <v>439.5898848482975</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>500.68286184544479</v>
+        <v>496.413133313376</v>
       </c>
       <c r="C8">
-        <v>511.878657046998</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D8">
-        <v>481.04173206397451</v>
+        <v>513.7638743357444</v>
       </c>
       <c r="E8">
-        <v>462.3286354642666</v>
+        <v>483.256574976819</v>
       </c>
       <c r="F8">
-        <v>454.21466400743151</v>
+        <v>463.2203610988426</v>
       </c>
       <c r="G8">
-        <v>451.26458745283992</v>
+        <v>454.6666959359249</v>
       </c>
       <c r="H8">
-        <v>455.07636453205907</v>
+        <v>449.9374156883161</v>
       </c>
       <c r="I8">
-        <v>450.94501928580848</v>
+        <v>454.956648248927</v>
       </c>
       <c r="J8">
-        <v>444.71106996932031</v>
+        <v>450.9051975594812</v>
       </c>
       <c r="K8">
-        <v>476.13392587190481</v>
+        <v>443.4994166009018</v>
       </c>
       <c r="L8">
-        <v>495.82211953757081</v>
+        <v>474.1396753152953</v>
       </c>
       <c r="M8">
-        <v>494.0795760449891</v>
+        <v>491.4767403118411</v>
       </c>
       <c r="N8">
-        <v>486.00711339476601</v>
+        <v>488.7394289316883</v>
       </c>
       <c r="O8">
-        <v>472.88926406117571</v>
+        <v>481.2603381294646</v>
       </c>
       <c r="P8">
-        <v>481.62725631612358</v>
+        <v>467.3764584841733</v>
       </c>
       <c r="Q8">
-        <v>480.92324540911659</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>477.0785583480389</v>
+      </c>
+      <c r="R8">
+        <v>475.9196434152768</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>497.51230710727617</v>
+        <v>504.3538445012761</v>
       </c>
       <c r="C9">
-        <v>512.12050904836906</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D9">
-        <v>482.25235722182151</v>
+        <v>513.5849744241691</v>
       </c>
       <c r="E9">
-        <v>463.48465050820289</v>
+        <v>483.3964952354854</v>
       </c>
       <c r="F9">
-        <v>456.45285764071258</v>
+        <v>464.0592603750109</v>
       </c>
       <c r="G9">
-        <v>452.98304825713711</v>
+        <v>456.6245873278015</v>
       </c>
       <c r="H9">
-        <v>455.34365566071409</v>
+        <v>453.4306691387594</v>
       </c>
       <c r="I9">
-        <v>451.51252122426303</v>
+        <v>457.0911025817116</v>
       </c>
       <c r="J9">
-        <v>445.69998360630569</v>
+        <v>453.5180193073614</v>
       </c>
       <c r="K9">
-        <v>467.07814070711242</v>
+        <v>445.4782435808531</v>
       </c>
       <c r="L9">
-        <v>483.90827712461379</v>
+        <v>467.4214945707236</v>
       </c>
       <c r="M9">
-        <v>493.22922653866658</v>
+        <v>485.6459934940389</v>
       </c>
       <c r="N9">
-        <v>485.01938675868479</v>
+        <v>492.8052504066439</v>
       </c>
       <c r="O9">
-        <v>467.68045573769598</v>
+        <v>484.5506290704702</v>
       </c>
       <c r="P9">
-        <v>473.40930277924957</v>
+        <v>467.498987287761</v>
       </c>
       <c r="Q9">
-        <v>478.18540954020631</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>473.0568284775364</v>
+      </c>
+      <c r="R9">
+        <v>477.5926051103096</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>496.08797092021769</v>
+        <v>497.0742636030372</v>
       </c>
       <c r="C10">
-        <v>511.83506971480227</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D10">
-        <v>480.95038146190473</v>
+        <v>512.0208471570277</v>
       </c>
       <c r="E10">
-        <v>459.85856613762752</v>
+        <v>481.3990938865708</v>
       </c>
       <c r="F10">
-        <v>451.93260296028251</v>
+        <v>461.1356287726532</v>
       </c>
       <c r="G10">
-        <v>449.69086457692129</v>
+        <v>453.6190157185554</v>
       </c>
       <c r="H10">
-        <v>452.47744969521841</v>
+        <v>450.4190436546201</v>
       </c>
       <c r="I10">
-        <v>448.66865383119142</v>
+        <v>453.6620988195705</v>
       </c>
       <c r="J10">
-        <v>440.86686082446778</v>
+        <v>450.7479287660628</v>
       </c>
       <c r="K10">
-        <v>461.28059878397289</v>
+        <v>443.3935081923766</v>
       </c>
       <c r="L10">
-        <v>477.17548082304029</v>
+        <v>465.8611070415321</v>
       </c>
       <c r="M10">
-        <v>488.62809740723168</v>
+        <v>483.0490694710487</v>
       </c>
       <c r="N10">
-        <v>480.66873762040302</v>
+        <v>494.0078877097671</v>
       </c>
       <c r="O10">
-        <v>463.94572011910839</v>
+        <v>485.764542826838</v>
       </c>
       <c r="P10">
-        <v>466.78509452252939</v>
+        <v>467.2720041868403</v>
       </c>
       <c r="Q10">
-        <v>473.77451240295341</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>470.0184923051688</v>
+      </c>
+      <c r="R10">
+        <v>475.3718449029639</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>500.43258441927901</v>
+        <v>499.0092208579512</v>
       </c>
       <c r="C11">
-        <v>512.34039007145361</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D11">
-        <v>481.51576551307039</v>
+        <v>512.686330953521</v>
       </c>
       <c r="E11">
-        <v>461.92726714387021</v>
+        <v>482.2363948833178</v>
       </c>
       <c r="F11">
-        <v>454.78152521889342</v>
+        <v>463.3523139382189</v>
       </c>
       <c r="G11">
-        <v>453.45662596087891</v>
+        <v>455.2088352410458</v>
       </c>
       <c r="H11">
-        <v>457.15376056170612</v>
+        <v>453.168466133038</v>
       </c>
       <c r="I11">
-        <v>454.10344348977799</v>
+        <v>455.5543445260534</v>
       </c>
       <c r="J11">
-        <v>445.3393015864732</v>
+        <v>451.1373747067681</v>
       </c>
       <c r="K11">
-        <v>465.8978711841047</v>
+        <v>444.001870442683</v>
       </c>
       <c r="L11">
-        <v>483.35055845426251</v>
+        <v>464.8209280103904</v>
       </c>
       <c r="M11">
-        <v>489.74587997395139</v>
+        <v>483.4642532726415</v>
       </c>
       <c r="N11">
-        <v>481.83761568974131</v>
+        <v>491.5672859532628</v>
       </c>
       <c r="O11">
-        <v>468.92590121808797</v>
+        <v>484.9943581575806</v>
       </c>
       <c r="P11">
-        <v>478.5532290056226</v>
+        <v>474.037982644235</v>
       </c>
       <c r="Q11">
-        <v>469.08896617356572</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>483.2103578074194</v>
+      </c>
+      <c r="R11">
+        <v>470.7811770427559</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>466.0665148272368</v>
+        <v>467.4257691464074</v>
       </c>
       <c r="C12">
-        <v>464.21494373974713</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D12">
-        <v>460.85066048471242</v>
+        <v>463.9883157627756</v>
       </c>
       <c r="E12">
-        <v>459.24412827600878</v>
+        <v>459.6082674383417</v>
       </c>
       <c r="F12">
-        <v>459.93349276695437</v>
+        <v>457.117201418113</v>
       </c>
       <c r="G12">
-        <v>455.56926236100799</v>
+        <v>456.7874838923244</v>
       </c>
       <c r="H12">
-        <v>454.50135848373378</v>
+        <v>453.3019615384342</v>
       </c>
       <c r="I12">
-        <v>454.94574491043448</v>
+        <v>455.16185055997</v>
       </c>
       <c r="J12">
-        <v>458.79402729231953</v>
+        <v>456.7996536358551</v>
       </c>
       <c r="K12">
-        <v>464.7907242753293</v>
+        <v>462.4223310171142</v>
       </c>
       <c r="L12">
-        <v>472.77090196203068</v>
+        <v>467.163936793437</v>
       </c>
       <c r="M12">
-        <v>484.4654059161507</v>
+        <v>475.4545398127781</v>
       </c>
       <c r="N12">
-        <v>496.86700769245363</v>
+        <v>491.5907846046875</v>
       </c>
       <c r="O12">
-        <v>498.54190370465659</v>
+        <v>501.3919847218171</v>
       </c>
       <c r="P12">
-        <v>508.82968611592241</v>
+        <v>505.8844417139989</v>
       </c>
       <c r="Q12">
-        <v>507.63613173215589</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>513.7467272765283</v>
+      </c>
+      <c r="R12">
+        <v>514.0762882126486</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>464.79792227437412</v>
+        <v>465.8049457916955</v>
       </c>
       <c r="C13">
-        <v>464.47811087365483</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D13">
-        <v>454.7938175627537</v>
+        <v>463.0267369412605</v>
       </c>
       <c r="E13">
-        <v>450.50481810041379</v>
+        <v>453.4788821873008</v>
       </c>
       <c r="F13">
-        <v>448.82125161474443</v>
+        <v>449.4998634854154</v>
       </c>
       <c r="G13">
-        <v>453.48835596401591</v>
+        <v>447.6249544676804</v>
       </c>
       <c r="H13">
-        <v>459.03057118572389</v>
+        <v>454.0968286000318</v>
       </c>
       <c r="I13">
-        <v>461.28631525909952</v>
+        <v>459.8216494250984</v>
       </c>
       <c r="J13">
-        <v>470.93767009991029</v>
+        <v>461.9380009417238</v>
       </c>
       <c r="K13">
-        <v>477.14357962737972</v>
+        <v>472.3715815843445</v>
       </c>
       <c r="L13">
-        <v>489.1220510304758</v>
+        <v>477.770516323173</v>
       </c>
       <c r="M13">
-        <v>493.90410325390121</v>
+        <v>491.4450793849335</v>
       </c>
       <c r="N13">
-        <v>497.38646573175731</v>
+        <v>496.5546071746873</v>
       </c>
       <c r="O13">
-        <v>503.34131085242359</v>
+        <v>500.9179562716608</v>
       </c>
       <c r="P13">
-        <v>510.47300327772939</v>
+        <v>506.9943936379575</v>
       </c>
       <c r="Q13">
-        <v>526.10575093329578</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>514.779038899826</v>
+      </c>
+      <c r="R13">
+        <v>527.3850495589836</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>436.50457018208948</v>
+        <v>435.6114911988964</v>
       </c>
       <c r="C14">
-        <v>535.1004677312302</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D14">
-        <v>470.97797952380472</v>
+        <v>536.371750377863</v>
       </c>
       <c r="E14">
-        <v>434.90732072224279</v>
+        <v>471.2025677515224</v>
       </c>
       <c r="F14">
-        <v>411.83010243698641</v>
+        <v>435.7392956856969</v>
       </c>
       <c r="G14">
-        <v>401.77932815540271</v>
+        <v>413.8501411739301</v>
       </c>
       <c r="H14">
-        <v>398.63998650876852</v>
+        <v>404.3379835361318</v>
       </c>
       <c r="I14">
-        <v>404.52534655901701</v>
+        <v>400.3430344559607</v>
       </c>
       <c r="J14">
-        <v>414.2091241301016</v>
+        <v>407.627488657039</v>
       </c>
       <c r="K14">
-        <v>423.7508820888936</v>
+        <v>416.2829555079836</v>
       </c>
       <c r="L14">
-        <v>426.63063689245621</v>
+        <v>425.2242869840163</v>
       </c>
       <c r="M14">
-        <v>463.20381300199608</v>
+        <v>426.4507046938137</v>
       </c>
       <c r="N14">
-        <v>465.41504197906738</v>
+        <v>464.2136546585024</v>
       </c>
       <c r="O14">
-        <v>453.29646201332201</v>
+        <v>466.9120567516887</v>
       </c>
       <c r="P14">
-        <v>446.9983543725121</v>
+        <v>453.5023832208273</v>
       </c>
       <c r="Q14">
-        <v>439.28781248532732</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>449.7964796215254</v>
+      </c>
+      <c r="R14">
+        <v>442.3765939491045</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>435.30842350872388</v>
+        <v>436.1300606861767</v>
       </c>
       <c r="C15">
-        <v>536.86664574287499</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D15">
-        <v>472.97058468915782</v>
+        <v>535.8121502188588</v>
       </c>
       <c r="E15">
-        <v>436.33893897463003</v>
+        <v>471.0376028971633</v>
       </c>
       <c r="F15">
-        <v>413.87851526499389</v>
+        <v>434.986106099574</v>
       </c>
       <c r="G15">
-        <v>404.09124512882238</v>
+        <v>412.9731758121717</v>
       </c>
       <c r="H15">
-        <v>399.93682034033839</v>
+        <v>403.4638334069371</v>
       </c>
       <c r="I15">
-        <v>408.30850992111351</v>
+        <v>398.7954586419285</v>
       </c>
       <c r="J15">
-        <v>416.67068759196462</v>
+        <v>406.7112986652407</v>
       </c>
       <c r="K15">
-        <v>423.70797819777471</v>
+        <v>414.4306258687944</v>
       </c>
       <c r="L15">
-        <v>426.38136624917649</v>
+        <v>422.789008785165</v>
       </c>
       <c r="M15">
-        <v>460.34191814747942</v>
+        <v>424.1369974611897</v>
       </c>
       <c r="N15">
-        <v>466.83378260998722</v>
+        <v>458.0022212742699</v>
       </c>
       <c r="O15">
-        <v>455.94448904828471</v>
+        <v>464.920872454448</v>
       </c>
       <c r="P15">
-        <v>451.10151152964028</v>
+        <v>455.0092832551119</v>
       </c>
       <c r="Q15">
-        <v>442.50740547851052</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>449.1265025386588</v>
+      </c>
+      <c r="R15">
+        <v>440.7636421207571</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>432.83482077468909</v>
+        <v>437.0215417420524</v>
       </c>
       <c r="C16">
-        <v>534.4808822587795</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D16">
-        <v>470.17664679531367</v>
+        <v>536.0896239490461</v>
       </c>
       <c r="E16">
-        <v>434.64200208637072</v>
+        <v>471.049439603048</v>
       </c>
       <c r="F16">
-        <v>412.93863967837382</v>
+        <v>434.7218334038164</v>
       </c>
       <c r="G16">
-        <v>402.59193218759452</v>
+        <v>412.354674884814</v>
       </c>
       <c r="H16">
-        <v>397.45514469446653</v>
+        <v>402.4628307902762</v>
       </c>
       <c r="I16">
-        <v>405.66690725715358</v>
+        <v>397.8937235059063</v>
       </c>
       <c r="J16">
-        <v>412.57925855426799</v>
+        <v>405.9260518706758</v>
       </c>
       <c r="K16">
-        <v>420.26013819429897</v>
+        <v>413.51556218948</v>
       </c>
       <c r="L16">
-        <v>422.25359024177538</v>
+        <v>422.0335221333613</v>
       </c>
       <c r="M16">
-        <v>455.58057296757079</v>
+        <v>422.6575758134122</v>
       </c>
       <c r="N16">
-        <v>460.35630005097312</v>
+        <v>456.1249298348915</v>
       </c>
       <c r="O16">
-        <v>449.13938001434587</v>
+        <v>461.8048554253467</v>
       </c>
       <c r="P16">
-        <v>445.62318394656228</v>
+        <v>450.8384280723795</v>
       </c>
       <c r="Q16">
-        <v>437.92961973582129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>448.5499495839545</v>
+      </c>
+      <c r="R16">
+        <v>441.3159917802673</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>431.49721744561373</v>
+        <v>435.0839192925826</v>
       </c>
       <c r="C17">
-        <v>535.72798576574667</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D17">
-        <v>471.62998235712053</v>
+        <v>536.1935918525166</v>
       </c>
       <c r="E17">
-        <v>434.60245407278228</v>
+        <v>471.9126671205115</v>
       </c>
       <c r="F17">
-        <v>412.38584172219038</v>
+        <v>437.4723577061835</v>
       </c>
       <c r="G17">
-        <v>402.71996536078228</v>
+        <v>414.822188281544</v>
       </c>
       <c r="H17">
-        <v>397.88372294657182</v>
+        <v>404.5398779275287</v>
       </c>
       <c r="I17">
-        <v>404.84351489300337</v>
+        <v>399.9822414296341</v>
       </c>
       <c r="J17">
-        <v>411.66230019730409</v>
+        <v>406.8773824729873</v>
       </c>
       <c r="K17">
-        <v>419.92005875091309</v>
+        <v>415.9314391651192</v>
       </c>
       <c r="L17">
-        <v>420.98393381348183</v>
+        <v>423.9264080064751</v>
       </c>
       <c r="M17">
-        <v>452.88556742007381</v>
+        <v>424.3194010869175</v>
       </c>
       <c r="N17">
-        <v>457.71014809877909</v>
+        <v>458.2605421408148</v>
       </c>
       <c r="O17">
-        <v>444.98765164592987</v>
+        <v>460.5827667482755</v>
       </c>
       <c r="P17">
-        <v>440.47301716694898</v>
+        <v>448.5009410726905</v>
       </c>
       <c r="Q17">
-        <v>432.83790146123789</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>444.4002825594827</v>
+      </c>
+      <c r="R17">
+        <v>435.6467408541781</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>468.56683539956128</v>
+        <v>469.2173534082174</v>
       </c>
       <c r="C18">
-        <v>463.89457257977699</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D18">
-        <v>461.02004302389702</v>
+        <v>462.0655669293012</v>
       </c>
       <c r="E18">
-        <v>462.20844623973471</v>
+        <v>459.7834352996472</v>
       </c>
       <c r="F18">
-        <v>462.254308450579</v>
+        <v>459.7501648082691</v>
       </c>
       <c r="G18">
-        <v>451.84864351018291</v>
+        <v>460.8440555468921</v>
       </c>
       <c r="H18">
-        <v>459.09358874451061</v>
+        <v>452.1090002001566</v>
       </c>
       <c r="I18">
-        <v>455.10654569007528</v>
+        <v>459.0617965887047</v>
       </c>
       <c r="J18">
-        <v>454.40113710673171</v>
+        <v>452.1983302389351</v>
       </c>
       <c r="K18">
-        <v>454.02581339133519</v>
+        <v>453.8283529598361</v>
       </c>
       <c r="L18">
-        <v>453.51867925571901</v>
+        <v>453.3382418275637</v>
       </c>
       <c r="M18">
-        <v>452.73306439175838</v>
+        <v>453.3199758339269</v>
       </c>
       <c r="N18">
-        <v>458.56382159345043</v>
+        <v>453.0969394429984</v>
       </c>
       <c r="O18">
-        <v>460.08531725457738</v>
+        <v>458.157660015507</v>
       </c>
       <c r="P18">
-        <v>469.80106542311552</v>
+        <v>459.0361313494711</v>
       </c>
       <c r="Q18">
-        <v>465.00436795256633</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>467.4844535168652</v>
+      </c>
+      <c r="R18">
+        <v>462.5543840432413</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>467.18844369378718</v>
+        <v>464.5335605630697</v>
       </c>
       <c r="C19">
-        <v>461.95601063464829</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D19">
-        <v>456.80103595467722</v>
+        <v>461.0282643003443</v>
       </c>
       <c r="E19">
-        <v>453.81438895694629</v>
+        <v>456.1102837627219</v>
       </c>
       <c r="F19">
-        <v>460.64106918578932</v>
+        <v>452.7159040069718</v>
       </c>
       <c r="G19">
-        <v>452.42918281881367</v>
+        <v>459.3749099478213</v>
       </c>
       <c r="H19">
-        <v>455.45409171410319</v>
+        <v>450.4198645940622</v>
       </c>
       <c r="I19">
-        <v>450.43653142461852</v>
+        <v>453.4617713460436</v>
       </c>
       <c r="J19">
-        <v>453.46371874163941</v>
+        <v>447.4828162694753</v>
       </c>
       <c r="K19">
-        <v>453.01366579114813</v>
+        <v>452.4024517205492</v>
       </c>
       <c r="L19">
-        <v>446.17605201200348</v>
+        <v>451.6134559201718</v>
       </c>
       <c r="M19">
-        <v>458.76210730594403</v>
+        <v>444.820011302546</v>
       </c>
       <c r="N19">
-        <v>465.61998416301788</v>
+        <v>457.1964209832025</v>
       </c>
       <c r="O19">
-        <v>467.03632625313088</v>
+        <v>466.2449986395129</v>
       </c>
       <c r="P19">
-        <v>470.27571007791869</v>
+        <v>465.0077379479257</v>
       </c>
       <c r="Q19">
-        <v>464.95486087657338</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>469.1561654268131</v>
+      </c>
+      <c r="R19">
+        <v>463.1807088577915</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>467.37476933451421</v>
+        <v>472.2052584343617</v>
       </c>
       <c r="C20">
-        <v>461.71566659483102</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D20">
-        <v>455.64997346547602</v>
+        <v>462.3450064816798</v>
       </c>
       <c r="E20">
-        <v>448.0646119495604</v>
+        <v>457.3692258476314</v>
       </c>
       <c r="F20">
-        <v>459.82566515389072</v>
+        <v>451.9041781641003</v>
       </c>
       <c r="G20">
-        <v>459.73226302040757</v>
+        <v>461.9809337160123</v>
       </c>
       <c r="H20">
-        <v>451.24498829902001</v>
+        <v>461.6311087970208</v>
       </c>
       <c r="I20">
-        <v>438.38899642015889</v>
+        <v>452.6883832294253</v>
       </c>
       <c r="J20">
-        <v>448.41081252578869</v>
+        <v>443.0848596957694</v>
       </c>
       <c r="K20">
-        <v>444.61183245734611</v>
+        <v>452.2263842792978</v>
       </c>
       <c r="L20">
-        <v>445.27296319319299</v>
+        <v>448.5816600354838</v>
       </c>
       <c r="M20">
-        <v>452.41402802259569</v>
+        <v>449.2762189283682</v>
       </c>
       <c r="N20">
-        <v>464.0138994992289</v>
+        <v>457.5619557383089</v>
       </c>
       <c r="O20">
-        <v>465.40331416481001</v>
+        <v>468.0635374960912</v>
       </c>
       <c r="P20">
-        <v>451.60028821174262</v>
+        <v>471.1628293365198</v>
       </c>
       <c r="Q20">
-        <v>451.59788424098917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>456.9186820004729</v>
+      </c>
+      <c r="R20">
+        <v>456.8022554331638</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>473.14205429726189</v>
+        <v>472.9175074454554</v>
       </c>
       <c r="C21">
-        <v>508.62252728577442</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D21">
-        <v>464.52182146172612</v>
+        <v>510.1412795893353</v>
       </c>
       <c r="E21">
-        <v>459.6688935697947</v>
+        <v>464.5457819525973</v>
       </c>
       <c r="F21">
-        <v>453.01964445194949</v>
+        <v>459.3489211842627</v>
       </c>
       <c r="G21">
-        <v>457.08390043449799</v>
+        <v>450.951270677467</v>
       </c>
       <c r="H21">
-        <v>461.52342589132189</v>
+        <v>457.4553094569558</v>
       </c>
       <c r="I21">
-        <v>490.34712356466503</v>
+        <v>461.939357989414</v>
       </c>
       <c r="J21">
-        <v>497.89260846917023</v>
+        <v>489.6024586275856</v>
       </c>
       <c r="K21">
-        <v>500.80113218968188</v>
+        <v>497.390880532507</v>
       </c>
       <c r="L21">
-        <v>510.43717155408581</v>
+        <v>499.6984184158435</v>
       </c>
       <c r="M21">
-        <v>525.42481351137042</v>
+        <v>510.7735578656125</v>
       </c>
       <c r="N21">
-        <v>540.31038125592113</v>
+        <v>527.1272383644184</v>
       </c>
       <c r="O21">
-        <v>559.71864762980044</v>
+        <v>542.2789889720494</v>
       </c>
       <c r="P21">
-        <v>585.15707878054718</v>
+        <v>561.4739316523388</v>
       </c>
       <c r="Q21">
-        <v>611.06655250936535</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>586.5074636124821</v>
+      </c>
+      <c r="R21">
+        <v>612.6749126911182</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>473.73069670114182</v>
+        <v>471.9694978976998</v>
       </c>
       <c r="C22">
-        <v>509.42805406559461</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D22">
-        <v>464.74004294753951</v>
+        <v>510.1781361851442</v>
       </c>
       <c r="E22">
-        <v>460.52345902404238</v>
+        <v>465.6038951850333</v>
       </c>
       <c r="F22">
-        <v>455.74226508763462</v>
+        <v>461.6036198688245</v>
       </c>
       <c r="G22">
-        <v>459.78482484620929</v>
+        <v>454.8765095101023</v>
       </c>
       <c r="H22">
-        <v>458.43282182051081</v>
+        <v>458.4046875222202</v>
       </c>
       <c r="I22">
-        <v>490.34895877900641</v>
+        <v>456.9738172171489</v>
       </c>
       <c r="J22">
-        <v>503.45515064400769</v>
+        <v>488.771116662997</v>
       </c>
       <c r="K22">
-        <v>504.65674554545109</v>
+        <v>500.0894442703606</v>
       </c>
       <c r="L22">
-        <v>511.75375564338049</v>
+        <v>500.1452426727511</v>
       </c>
       <c r="M22">
-        <v>527.91129915612726</v>
+        <v>506.8928905654241</v>
       </c>
       <c r="N22">
-        <v>542.83824524155727</v>
+        <v>524.428196837174</v>
       </c>
       <c r="O22">
-        <v>560.76584495071768</v>
+        <v>540.5509767735884</v>
       </c>
       <c r="P22">
-        <v>586.96964146397738</v>
+        <v>558.5611235182384</v>
       </c>
       <c r="Q22">
-        <v>608.23229312793001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>586.3366806075491</v>
+      </c>
+      <c r="R22">
+        <v>605.2011142507848</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>465.68489508706239</v>
+        <v>463.6775980240222</v>
       </c>
       <c r="C23">
-        <v>465.31466487857062</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D23">
-        <v>482.28365390251412</v>
+        <v>463.1205123504977</v>
       </c>
       <c r="E23">
-        <v>467.54359137245888</v>
+        <v>476.987366252879</v>
       </c>
       <c r="F23">
-        <v>459.55496591468449</v>
+        <v>462.7096226457002</v>
       </c>
       <c r="G23">
-        <v>479.75726113385872</v>
+        <v>457.695419297987</v>
       </c>
       <c r="H23">
-        <v>502.25828312334181</v>
+        <v>474.6917191820036</v>
       </c>
       <c r="I23">
-        <v>533.16821625900911</v>
+        <v>496.6206676582943</v>
       </c>
       <c r="J23">
-        <v>538.00937425099403</v>
+        <v>530.2716576336384</v>
       </c>
       <c r="K23">
-        <v>558.11264453012586</v>
+        <v>535.994970809202</v>
       </c>
       <c r="L23">
-        <v>571.94671293864269</v>
+        <v>554.624988673041</v>
       </c>
       <c r="M23">
-        <v>588.62600697837922</v>
+        <v>566.4986310949233</v>
       </c>
       <c r="N23">
-        <v>595.38242244202991</v>
+        <v>581.3080074134451</v>
       </c>
       <c r="O23">
-        <v>613.65847947098143</v>
+        <v>589.4525367310763</v>
       </c>
       <c r="P23">
-        <v>631.02843280522461</v>
+        <v>605.9110343941016</v>
       </c>
       <c r="Q23">
-        <v>651.88256156458408</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>624.079158757303</v>
+      </c>
+      <c r="R23">
+        <v>645.0392947198256</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>641.03112189132821</v>
+        <v>417.857829208362</v>
       </c>
       <c r="C24">
-        <v>641.03112189132821</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D24">
-        <v>664.60678386882876</v>
+        <v>454.4036990659282</v>
       </c>
       <c r="E24">
-        <v>658.10322895829472</v>
+        <v>420.6929937360368</v>
       </c>
       <c r="F24">
-        <v>695.53919196981997</v>
+        <v>400.0635760452006</v>
       </c>
       <c r="G24">
-        <v>781.67735907646966</v>
+        <v>386.6424058744484</v>
       </c>
       <c r="H24">
-        <v>748.48342758387048</v>
+        <v>401.8156067550989</v>
       </c>
       <c r="I24">
-        <v>768.21324376973689</v>
+        <v>410.5987863341219</v>
       </c>
       <c r="J24">
-        <v>784.41559042767756</v>
+        <v>408.505371657075</v>
       </c>
       <c r="K24">
-        <v>796.948396552536</v>
+        <v>420.5440375194717</v>
       </c>
       <c r="L24">
-        <v>814.56850254736605</v>
+        <v>401.0062778816865</v>
       </c>
       <c r="M24">
-        <v>830.76305360876665</v>
+        <v>392.463267827407</v>
       </c>
       <c r="N24">
-        <v>831.447087289514</v>
+        <v>412.2655627916717</v>
       </c>
       <c r="O24">
-        <v>828.17328902387715</v>
+        <v>421.4466672261423</v>
       </c>
       <c r="P24">
-        <v>836.75652442945375</v>
+        <v>439.6686577230803</v>
       </c>
       <c r="Q24">
-        <v>841.84694317261983</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>452.5477611969476</v>
+      </c>
+      <c r="R24">
+        <v>473.8238609985443</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>648.32600220972859</v>
+        <v>385.4967531411251</v>
       </c>
       <c r="C25">
-        <v>648.32600220972859</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D25">
-        <v>665.24361505869308</v>
+        <v>454.014899013197</v>
       </c>
       <c r="E25">
-        <v>679.95629211148503</v>
+        <v>417.5220326441717</v>
       </c>
       <c r="F25">
-        <v>711.796850862317</v>
+        <v>391.1787464128244</v>
       </c>
       <c r="G25">
-        <v>736.78732210021747</v>
+        <v>372.6055269122168</v>
       </c>
       <c r="H25">
-        <v>781.01599697978338</v>
+        <v>376.9009146364446</v>
       </c>
       <c r="I25">
-        <v>812.90087483286788</v>
+        <v>368.9132081442601</v>
       </c>
       <c r="J25">
-        <v>835.59572262257586</v>
+        <v>373.0541890901974</v>
       </c>
       <c r="K25">
-        <v>838.6020409492611</v>
+        <v>378.5411033234756</v>
       </c>
       <c r="L25">
-        <v>836.88671296832013</v>
+        <v>356.914038427993</v>
       </c>
       <c r="M25">
-        <v>861.81240237265399</v>
+        <v>354.3826540424465</v>
       </c>
       <c r="N25">
-        <v>886.81635896928708</v>
+        <v>355.8285979890478</v>
       </c>
       <c r="O25">
-        <v>907.89734071404905</v>
+        <v>362.8052461419617</v>
       </c>
       <c r="P25">
-        <v>911.28581322431592</v>
+        <v>374.8778888448053</v>
       </c>
       <c r="Q25">
-        <v>915.23697543243247</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>386.4314646725297</v>
+      </c>
+      <c r="R25">
+        <v>405.4781893558772</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>645.73047409516084</v>
+        <v>427.5275666134603</v>
       </c>
       <c r="C26">
-        <v>643.98854763401187</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D26">
-        <v>655.15746626808129</v>
+        <v>446.4537403247675</v>
       </c>
       <c r="E26">
-        <v>658.24066129660787</v>
+        <v>428.1746616645487</v>
       </c>
       <c r="F26">
-        <v>689.48962111344269</v>
+        <v>405.7720109316267</v>
       </c>
       <c r="G26">
-        <v>717.33730773246918</v>
+        <v>391.0209543063229</v>
       </c>
       <c r="H26">
-        <v>724.58645745207605</v>
+        <v>402.1347284308487</v>
       </c>
       <c r="I26">
-        <v>743.4132303588824</v>
+        <v>390.0273463408675</v>
       </c>
       <c r="J26">
-        <v>732.84032989797004</v>
+        <v>396.8034374538444</v>
       </c>
       <c r="K26">
-        <v>716.46749441160819</v>
+        <v>397.9952979453064</v>
       </c>
       <c r="L26">
-        <v>700.50582738783737</v>
+        <v>396.0538914194305</v>
       </c>
       <c r="M26">
-        <v>749.47849671917606</v>
+        <v>384.637606842472</v>
       </c>
       <c r="N26">
-        <v>798.19422232772342</v>
+        <v>389.8145253946511</v>
       </c>
       <c r="O26">
-        <v>783.30135729081132</v>
+        <v>391.2219808258862</v>
       </c>
       <c r="P26">
-        <v>793.03130662868557</v>
+        <v>403.4643252452736</v>
       </c>
       <c r="Q26">
-        <v>798.38412076166912</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>421.0013502393017</v>
+      </c>
+      <c r="R26">
+        <v>439.3571647586686</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>652.04715593512765</v>
+        <v>442.5885661290098</v>
       </c>
       <c r="C27">
-        <v>650.55420311333853</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D27">
-        <v>659.09816174066998</v>
+        <v>446.5954585388419</v>
       </c>
       <c r="E27">
-        <v>698.33873641640253</v>
+        <v>428.883804971875</v>
       </c>
       <c r="F27">
-        <v>684.34761508158954</v>
+        <v>406.1782912325314</v>
       </c>
       <c r="G27">
-        <v>719.28454748202716</v>
+        <v>391.3050711514596</v>
       </c>
       <c r="H27">
-        <v>713.59676121795189</v>
+        <v>400.4931626742621</v>
       </c>
       <c r="I27">
-        <v>690.19974738012547</v>
+        <v>394.4130846974396</v>
       </c>
       <c r="J27">
-        <v>688.35853920050317</v>
+        <v>397.8060549747122</v>
       </c>
       <c r="K27">
-        <v>712.62416444612109</v>
+        <v>401.639110127786</v>
       </c>
       <c r="L27">
-        <v>739.45946358213871</v>
+        <v>405.0703754657788</v>
       </c>
       <c r="M27">
-        <v>758.97156570297307</v>
+        <v>400.8411210731502</v>
       </c>
       <c r="N27">
-        <v>776.36975005317549</v>
+        <v>403.48193727087</v>
       </c>
       <c r="O27">
-        <v>755.52120397308317</v>
+        <v>401.9155460760708</v>
       </c>
       <c r="P27">
-        <v>783.84126824343798</v>
+        <v>406.7538055002026</v>
       </c>
       <c r="Q27">
-        <v>794.85180955868748</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>415.693918912473</v>
+      </c>
+      <c r="R27">
+        <v>412.0683471974633</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>417.11391842192182</v>
+        <v>401.0911318706792</v>
       </c>
       <c r="C28">
-        <v>454.35288355295393</v>
-      </c>
-      <c r="D28" s="2">
-        <v>420.99140365287172</v>
+        <v>674.4628817661144</v>
+      </c>
+      <c r="D28">
+        <v>454.9626807583912</v>
       </c>
       <c r="E28">
-        <v>401.92555041048257</v>
+        <v>420.5323710046362</v>
       </c>
       <c r="F28">
-        <v>387.64020479773671</v>
+        <v>396.1065683472664</v>
       </c>
       <c r="G28">
-        <v>404.08484638341417</v>
+        <v>376.9233298718062</v>
       </c>
       <c r="H28">
-        <v>410.5478758523484</v>
+        <v>384.1805708851517</v>
       </c>
       <c r="I28">
-        <v>412.10844827858051</v>
+        <v>376.902956874929</v>
       </c>
       <c r="J28">
-        <v>420.20648358030962</v>
+        <v>382.9457198695428</v>
       </c>
       <c r="K28">
-        <v>401.39998441856608</v>
+        <v>396.7800427144819</v>
       </c>
       <c r="L28">
-        <v>390.40248765360838</v>
+        <v>377.0840614677217</v>
       </c>
       <c r="M28">
-        <v>409.57802287526471</v>
+        <v>373.6768530027174</v>
       </c>
       <c r="N28">
-        <v>420.44442167836252</v>
+        <v>368.3363957749193</v>
       </c>
       <c r="O28">
-        <v>437.11018015020232</v>
+        <v>371.9518000812274</v>
       </c>
       <c r="P28">
-        <v>447.80218695655071</v>
+        <v>380.5050894800743</v>
       </c>
       <c r="Q28">
-        <v>468.12334705852481</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>386.7123746408466</v>
+      </c>
+      <c r="R28">
+        <v>404.8376175983335</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>392.64152691392371</v>
+        <v>398.0349995881376</v>
       </c>
       <c r="C29">
-        <v>454.95535593410392</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D29">
-        <v>420.19287174017228</v>
-      </c>
-      <c r="E29" s="2">
-        <v>394.31005875946522</v>
-      </c>
-      <c r="F29" s="2">
-        <v>375.13347614594642</v>
+        <v>454.5172434748189</v>
+      </c>
+      <c r="E29">
+        <v>419.5690790388916</v>
+      </c>
+      <c r="F29">
+        <v>393.6221811761776</v>
       </c>
       <c r="G29">
-        <v>379.38327894928449</v>
+        <v>373.4400796690148</v>
       </c>
       <c r="H29">
-        <v>371.92026150756459</v>
+        <v>377.5230874548175</v>
       </c>
       <c r="I29">
-        <v>375.43731480938391</v>
+        <v>371.9585595728657</v>
       </c>
       <c r="J29">
-        <v>381.18784686272232</v>
+        <v>373.5995168513316</v>
       </c>
       <c r="K29">
-        <v>358.74505907393183</v>
+        <v>385.6816825449143</v>
       </c>
       <c r="L29">
-        <v>359.68802183094698</v>
+        <v>369.4850942030654</v>
       </c>
       <c r="M29">
-        <v>359.22399587432483</v>
+        <v>366.8369537725122</v>
       </c>
       <c r="N29">
-        <v>367.71339024073461</v>
+        <v>361.7810214824981</v>
       </c>
       <c r="O29">
-        <v>377.93262150881208</v>
+        <v>366.5502289995323</v>
       </c>
       <c r="P29">
-        <v>391.99526198909768</v>
+        <v>375.6598426619492</v>
       </c>
       <c r="Q29">
-        <v>410.6608464986212</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>383.8373693036997</v>
+      </c>
+      <c r="R29">
+        <v>407.1525873591018</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>432.18454082566558</v>
+        <v>400.5737190050875</v>
       </c>
       <c r="C30">
-        <v>446.93096253180971</v>
-      </c>
-      <c r="D30" s="2">
-        <v>429.23865621410181</v>
-      </c>
-      <c r="E30" s="2">
-        <v>408.28030355533889</v>
+        <v>674.4628817661144</v>
+      </c>
+      <c r="D30">
+        <v>454.9261586998869</v>
+      </c>
+      <c r="E30">
+        <v>419.5386897838069</v>
       </c>
       <c r="F30">
-        <v>393.42998991632368</v>
+        <v>394.2060739291599</v>
       </c>
       <c r="G30">
-        <v>403.51711295608112</v>
+        <v>375.5255861264104</v>
       </c>
       <c r="H30">
-        <v>392.7838116315591</v>
+        <v>380.334313779312</v>
       </c>
       <c r="I30">
-        <v>398.75831986732379</v>
+        <v>375.4587028527262</v>
       </c>
       <c r="J30">
-        <v>402.34265304072551</v>
+        <v>379.1921945165994</v>
       </c>
       <c r="K30">
-        <v>398.89443386060992</v>
+        <v>393.8529925687659</v>
       </c>
       <c r="L30">
-        <v>387.20621324811071</v>
+        <v>374.4756345917835</v>
       </c>
       <c r="M30">
-        <v>392.70070625451359</v>
+        <v>372.2792194904397</v>
       </c>
       <c r="N30">
-        <v>394.36026737601202</v>
+        <v>364.9973766016576</v>
       </c>
       <c r="O30">
-        <v>407.95353179285001</v>
+        <v>368.58494805429</v>
       </c>
       <c r="P30">
-        <v>425.78793830611568</v>
+        <v>377.9538589178353</v>
       </c>
       <c r="Q30">
-        <v>445.34831190669541</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>386.2129925252801</v>
+      </c>
+      <c r="R30">
+        <v>410.0022433841282</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>439.916660716016</v>
+        <v>397.1785595005296</v>
       </c>
       <c r="C31">
-        <v>446.25685332989639</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D31">
-        <v>428.00431090256188</v>
-      </c>
-      <c r="E31" s="2">
-        <v>406.20413507774492</v>
+        <v>454.8280475775139</v>
+      </c>
+      <c r="E31">
+        <v>419.2285055710139</v>
       </c>
       <c r="F31">
-        <v>392.43886234259043</v>
+        <v>394.7923427358801</v>
       </c>
       <c r="G31">
-        <v>402.44525219678462</v>
+        <v>375.1270438189094</v>
       </c>
       <c r="H31">
-        <v>392.81899896058758</v>
+        <v>379.7076304006475</v>
       </c>
       <c r="I31">
-        <v>397.64879425958168</v>
+        <v>374.2084933586501</v>
       </c>
       <c r="J31">
-        <v>401.40185051799631</v>
+        <v>377.2349653785885</v>
       </c>
       <c r="K31">
-        <v>405.58369953967588</v>
+        <v>391.2631962001447</v>
       </c>
       <c r="L31">
-        <v>402.98959613552142</v>
+        <v>372.8467856604991</v>
       </c>
       <c r="M31">
-        <v>404.33361285308757</v>
+        <v>370.8810713068073</v>
       </c>
       <c r="N31">
-        <v>402.60185465000473</v>
+        <v>363.9209115136682</v>
       </c>
       <c r="O31">
-        <v>407.22462201324697</v>
+        <v>368.4484817467078</v>
       </c>
       <c r="P31">
-        <v>418.67945079117442</v>
+        <v>377.7861880893738</v>
       </c>
       <c r="Q31">
-        <v>413.91236261113642</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>381.9333375391192</v>
+      </c>
+      <c r="R31">
+        <v>403.073272121404</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>400.96716378854728</v>
+        <v>402.682359488858</v>
       </c>
       <c r="C32">
-        <v>454.58745341455511</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D32">
-        <v>419.76765223013939</v>
-      </c>
-      <c r="E32" s="2">
-        <v>395.05065535540871</v>
+        <v>454.22962067456</v>
+      </c>
+      <c r="E32">
+        <v>419.7634689386309</v>
       </c>
       <c r="F32">
-        <v>375.59849894971939</v>
+        <v>394.8324644961442</v>
       </c>
       <c r="G32">
-        <v>382.05596819475647</v>
+        <v>375.7896044629302</v>
       </c>
       <c r="H32">
-        <v>376.15980353830628</v>
+        <v>382.5457801384681</v>
       </c>
       <c r="I32">
-        <v>378.97671604167971</v>
+        <v>375.5708161556519</v>
       </c>
       <c r="J32">
-        <v>393.24910618321371</v>
+        <v>380.6407187862207</v>
       </c>
       <c r="K32">
-        <v>376.34964332668687</v>
+        <v>392.5552047205359</v>
       </c>
       <c r="L32">
-        <v>373.49721999711488</v>
+        <v>375.5521280628291</v>
       </c>
       <c r="M32">
-        <v>368.80976573715418</v>
+        <v>374.314293048723</v>
       </c>
       <c r="N32">
-        <v>372.14807004136122</v>
+        <v>371.7645308332075</v>
       </c>
       <c r="O32">
-        <v>381.45759133285941</v>
+        <v>375.711268213667</v>
       </c>
       <c r="P32">
-        <v>387.98914195321157</v>
+        <v>384.0856339787062</v>
       </c>
       <c r="Q32">
-        <v>408.82717930769928</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>388.0002983913172</v>
+      </c>
+      <c r="R32">
+        <v>408.4038264562361</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>395.2317956453316</v>
+        <v>400.4626667527838</v>
       </c>
       <c r="C33">
-        <v>454.35479705344562</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D33">
-        <v>419.47919136551212</v>
-      </c>
-      <c r="E33" s="2">
-        <v>394.17865294622499</v>
+        <v>454.3352132347982</v>
+      </c>
+      <c r="E33">
+        <v>419.7604468200263</v>
       </c>
       <c r="F33">
-        <v>375.22510966290889</v>
+        <v>394.9416449845829</v>
       </c>
       <c r="G33">
-        <v>380.93202094270038</v>
+        <v>375.5048183054828</v>
       </c>
       <c r="H33">
-        <v>375.64683849178778</v>
+        <v>380.8125506997399</v>
       </c>
       <c r="I33">
-        <v>378.52390682896032</v>
+        <v>374.9900716839197</v>
       </c>
       <c r="J33">
-        <v>392.29462071897279</v>
+        <v>379.366207691236</v>
       </c>
       <c r="K33">
-        <v>371.49872813614769</v>
+        <v>390.7288441260252</v>
       </c>
       <c r="L33">
-        <v>371.18959147725133</v>
+        <v>374.036101892898</v>
       </c>
       <c r="M33">
-        <v>365.10163733436212</v>
+        <v>375.0305581843531</v>
       </c>
       <c r="N33">
-        <v>370.11140564103079</v>
+        <v>369.8240419322151</v>
       </c>
       <c r="O33">
-        <v>379.0878622537503</v>
+        <v>375.4590129090991</v>
       </c>
       <c r="P33">
-        <v>388.39386737731752</v>
+        <v>383.0109557475621</v>
       </c>
       <c r="Q33">
-        <v>409.6554470329728</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>390.763282369735</v>
+      </c>
+      <c r="R33">
+        <v>412.0632720439659</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>399.56188354455992</v>
+        <v>401.4131673898835</v>
       </c>
       <c r="C34">
-        <v>454.58485216278427</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D34">
-        <v>419.65948253775872</v>
-      </c>
-      <c r="E34" s="2">
-        <v>394.47140508604411</v>
+        <v>455.175983770725</v>
+      </c>
+      <c r="E34">
+        <v>419.9712134516326</v>
       </c>
       <c r="F34">
-        <v>375.39589999821999</v>
+        <v>394.7880181441848</v>
       </c>
       <c r="G34">
-        <v>381.14983193607162</v>
+        <v>375.1277385582723</v>
       </c>
       <c r="H34">
-        <v>373.99400724046859</v>
+        <v>380.3598659852151</v>
       </c>
       <c r="I34">
-        <v>377.72907897455912</v>
+        <v>374.3117678742335</v>
       </c>
       <c r="J34">
-        <v>391.46347876150361</v>
+        <v>377.6514130938884</v>
       </c>
       <c r="K34">
-        <v>374.12215368890031</v>
+        <v>388.0543979451326</v>
       </c>
       <c r="L34">
-        <v>369.42594932350818</v>
+        <v>372.3477924361678</v>
       </c>
       <c r="M34">
-        <v>363.07040291816998</v>
+        <v>372.553400141891</v>
       </c>
       <c r="N34">
-        <v>367.69626117142531</v>
+        <v>368.5240254811125</v>
       </c>
       <c r="O34">
-        <v>378.35058988064412</v>
+        <v>371.0108719523019</v>
       </c>
       <c r="P34">
-        <v>384.4350769952344</v>
+        <v>379.8209760482898</v>
       </c>
       <c r="Q34">
-        <v>407.15350976276818</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>385.5619950871966</v>
+      </c>
+      <c r="R34">
+        <v>409.0366178177412</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>397.68640790429811</v>
+        <v>396.98681137432</v>
       </c>
       <c r="C35">
-        <v>454.59434071009929</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D35">
-        <v>419.62153585690658</v>
-      </c>
-      <c r="E35" s="2">
-        <v>395.03957505258319</v>
-      </c>
-      <c r="F35" s="2">
-        <v>375.1517488806968</v>
+        <v>454.6301399352674</v>
+      </c>
+      <c r="E35">
+        <v>419.4155064367116</v>
+      </c>
+      <c r="F35">
+        <v>394.1377078585551</v>
       </c>
       <c r="G35">
-        <v>380.00952750318038</v>
+        <v>375.29955001151</v>
       </c>
       <c r="H35">
-        <v>374.05625889170011</v>
+        <v>380.5819038640932</v>
       </c>
       <c r="I35">
-        <v>377.62989135615959</v>
+        <v>373.9515788674764</v>
       </c>
       <c r="J35">
-        <v>391.69791718197553</v>
+        <v>377.090107826772</v>
       </c>
       <c r="K35">
-        <v>372.65789633518432</v>
+        <v>388.5993433783734</v>
       </c>
       <c r="L35">
-        <v>370.45804011447359</v>
+        <v>372.7525509076789</v>
       </c>
       <c r="M35">
-        <v>363.70642690143961</v>
+        <v>372.0857445521083</v>
       </c>
       <c r="N35">
-        <v>367.54184103892698</v>
+        <v>368.3073780119965</v>
       </c>
       <c r="O35">
-        <v>375.96170479818818</v>
+        <v>370.7792280170302</v>
       </c>
       <c r="P35">
-        <v>382.98624340090589</v>
+        <v>378.6935414949828</v>
       </c>
       <c r="Q35">
-        <v>403.99498407472072</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>384.625135840412</v>
+      </c>
+      <c r="R35">
+        <v>405.5034153496995</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>402.3839255260354</v>
+        <v>398.5390740734898</v>
       </c>
       <c r="C36">
-        <v>454.71252475133662</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D36">
-        <v>419.17164315317848</v>
-      </c>
-      <c r="E36" s="2">
-        <v>394.35852015337139</v>
+        <v>455.1236787919731</v>
+      </c>
+      <c r="E36">
+        <v>420.0986185291508</v>
       </c>
       <c r="F36">
-        <v>375.30829370213308</v>
+        <v>394.9873726199933</v>
       </c>
       <c r="G36">
-        <v>379.28691771260452</v>
+        <v>375.8028733972127</v>
       </c>
       <c r="H36">
-        <v>373.42622212672501</v>
+        <v>380.2046784615714</v>
       </c>
       <c r="I36">
-        <v>377.11912975201687</v>
+        <v>374.7317311927181</v>
       </c>
       <c r="J36">
-        <v>387.85956149756419</v>
+        <v>378.5120576840812</v>
       </c>
       <c r="K36">
-        <v>371.07371942416182</v>
+        <v>392.0394492546559</v>
       </c>
       <c r="L36">
-        <v>370.95934979059581</v>
+        <v>373.6568738810643</v>
       </c>
       <c r="M36">
-        <v>369.2405289496171</v>
+        <v>372.2915364048804</v>
       </c>
       <c r="N36">
-        <v>372.86659007285368</v>
+        <v>365.677782634355</v>
       </c>
       <c r="O36">
-        <v>382.96395524886208</v>
+        <v>369.8035676662987</v>
       </c>
       <c r="P36">
-        <v>386.54807242743948</v>
+        <v>377.4389985261302</v>
       </c>
       <c r="Q36">
-        <v>405.94535585206989</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>380.3139074682961</v>
+      </c>
+      <c r="R36">
+        <v>404.5745557161792</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>399.00778191868289</v>
+        <v>417.4838929726462</v>
       </c>
       <c r="C37">
-        <v>455.19891906727759</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D37">
-        <v>420.25003534426253</v>
-      </c>
-      <c r="E37" s="2">
-        <v>394.18728491304972</v>
+        <v>445.371606976709</v>
+      </c>
+      <c r="E37">
+        <v>416.1417401891881</v>
       </c>
       <c r="F37">
-        <v>374.82250010017589</v>
+        <v>383.2474306844443</v>
       </c>
       <c r="G37">
-        <v>380.15029800757827</v>
+        <v>386.7562520075653</v>
       </c>
       <c r="H37">
-        <v>373.99300327912408</v>
+        <v>405.316353430359</v>
       </c>
       <c r="I37">
-        <v>376.54126070597238</v>
+        <v>435.2583478610986</v>
       </c>
       <c r="J37">
-        <v>390.1510981893565</v>
+        <v>430.6204261555252</v>
       </c>
       <c r="K37">
-        <v>372.60549989595722</v>
+        <v>438.599139335146</v>
       </c>
       <c r="L37">
-        <v>372.53663381943198</v>
+        <v>446.0788980543667</v>
       </c>
       <c r="M37">
-        <v>369.32097065219972</v>
+        <v>444.9825137639462</v>
       </c>
       <c r="N37">
-        <v>374.04049737948162</v>
+        <v>454.954235233346</v>
       </c>
       <c r="O37">
-        <v>384.15910538359577</v>
+        <v>455.2889282512741</v>
       </c>
       <c r="P37">
-        <v>390.66834341013691</v>
+        <v>464.4156595079851</v>
       </c>
       <c r="Q37">
-        <v>410.06779303581709</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>472.772441976074</v>
+      </c>
+      <c r="R37">
+        <v>477.1828630203867</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>400.31872936395678</v>
+        <v>408.4821940333237</v>
       </c>
       <c r="C38">
-        <v>454.50168822595958</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D38">
-        <v>419.0940750608948</v>
-      </c>
-      <c r="E38" s="2">
-        <v>394.2483261761808</v>
+        <v>444.8931746713318</v>
+      </c>
+      <c r="E38">
+        <v>411.2812825592911</v>
       </c>
       <c r="F38">
-        <v>374.93181851121528</v>
+        <v>379.801553215901</v>
       </c>
       <c r="G38">
-        <v>380.93826752299088</v>
+        <v>382.5388553443817</v>
       </c>
       <c r="H38">
-        <v>374.59310266236838</v>
+        <v>403.9957993867006</v>
       </c>
       <c r="I38">
-        <v>378.18287782757949</v>
+        <v>431.5959964718928</v>
       </c>
       <c r="J38">
-        <v>389.04785260037983</v>
+        <v>413.8227789266959</v>
       </c>
       <c r="K38">
-        <v>372.57701678108668</v>
+        <v>416.1761424749294</v>
       </c>
       <c r="L38">
-        <v>371.8902413018626</v>
+        <v>407.4904196056654</v>
       </c>
       <c r="M38">
-        <v>368.75985454649788</v>
+        <v>392.9430505960285</v>
       </c>
       <c r="N38">
-        <v>371.07742567717492</v>
+        <v>398.1043043708693</v>
       </c>
       <c r="O38">
-        <v>379.93458143302678</v>
+        <v>403.0865835417378</v>
       </c>
       <c r="P38">
-        <v>384.91451752343698</v>
+        <v>402.678097907548</v>
       </c>
       <c r="Q38">
-        <v>410.61190907525997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>413.9921187193607</v>
+      </c>
+      <c r="R38">
+        <v>434.31933739317</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>398.20276602278261</v>
+        <v>407.2760091623896</v>
       </c>
       <c r="C39">
-        <v>454.22150630178078</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D39">
-        <v>419.33818798743528</v>
-      </c>
-      <c r="E39" s="2">
-        <v>393.30670056955842</v>
+        <v>443.9473535860924</v>
+      </c>
+      <c r="E39">
+        <v>407.8623431695621</v>
       </c>
       <c r="F39">
-        <v>374.06415592560103</v>
+        <v>377.6961097615399</v>
       </c>
       <c r="G39">
-        <v>379.4616167728621</v>
+        <v>381.8203230602299</v>
       </c>
       <c r="H39">
-        <v>372.52244149791449</v>
+        <v>402.056454260972</v>
       </c>
       <c r="I39">
-        <v>377.7609621507105</v>
+        <v>426.5067435359364</v>
       </c>
       <c r="J39">
-        <v>390.09279067745263</v>
+        <v>408.1440920982296</v>
       </c>
       <c r="K39">
-        <v>371.9524733686053</v>
+        <v>412.3693920988381</v>
       </c>
       <c r="L39">
-        <v>370.83685830157748</v>
+        <v>406.9571978137749</v>
       </c>
       <c r="M39">
-        <v>368.12884488852961</v>
+        <v>399.9778675495195</v>
       </c>
       <c r="N39">
-        <v>371.68719568306551</v>
+        <v>405.770641758319</v>
       </c>
       <c r="O39">
-        <v>378.39680373614237</v>
+        <v>408.9523384401056</v>
       </c>
       <c r="P39">
-        <v>386.27425117468721</v>
+        <v>406.2587878519407</v>
       </c>
       <c r="Q39">
-        <v>409.3113403436015</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>408.3110040875446</v>
+      </c>
+      <c r="R39">
+        <v>424.4336629787824</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>399.24886028642891</v>
+        <v>462.6802197888602</v>
       </c>
       <c r="C40">
-        <v>454.21027395778401</v>
+        <v>674.4628817661144</v>
       </c>
       <c r="D40">
-        <v>419.32857559512053</v>
-      </c>
-      <c r="E40" s="2">
-        <v>395.26394255904722</v>
+        <v>464.5773778190814</v>
+      </c>
+      <c r="E40">
+        <v>473.7670929682205</v>
       </c>
       <c r="F40">
-        <v>375.81182708855567</v>
+        <v>445.1840538442613</v>
       </c>
       <c r="G40">
-        <v>381.66523885652771</v>
+        <v>418.4206876119301</v>
       </c>
       <c r="H40">
-        <v>376.13114751191023</v>
+        <v>414.9153258780143</v>
       </c>
       <c r="I40">
-        <v>379.89923135596871</v>
+        <v>414.8364896221329</v>
       </c>
       <c r="J40">
-        <v>394.68767060835279</v>
+        <v>422.0335898503946</v>
       </c>
       <c r="K40">
-        <v>375.03020441587108</v>
+        <v>425.8327235334772</v>
       </c>
       <c r="L40">
-        <v>372.83409769225841</v>
+        <v>430.3759571327887</v>
       </c>
       <c r="M40">
-        <v>365.17486437139081</v>
+        <v>445.8937733020907</v>
       </c>
       <c r="N40">
-        <v>369.8596923196846</v>
+        <v>463.112179066716</v>
       </c>
       <c r="O40">
-        <v>377.5640543624736</v>
+        <v>477.6248416319461</v>
       </c>
       <c r="P40">
-        <v>381.32464388476723</v>
+        <v>492.463716685851</v>
       </c>
       <c r="Q40">
-        <v>404.3354456482208</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>505.3561743489663</v>
+      </c>
+      <c r="R40">
+        <v>526.7733628506552</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>410.64034591029201</v>
+        <v>468.8433003371603</v>
       </c>
       <c r="C41">
-        <v>445.48078443916842</v>
-      </c>
-      <c r="D41" s="2">
-        <v>412.17703083713388</v>
+        <v>674.4628817661144</v>
+      </c>
+      <c r="D41">
+        <v>468.1540508779203</v>
       </c>
       <c r="E41">
-        <v>380.33324512804609</v>
+        <v>447.8476837735228</v>
       </c>
       <c r="F41">
-        <v>385.34733810404191</v>
+        <v>456.3654378446556</v>
       </c>
       <c r="G41">
-        <v>404.14102112601739</v>
+        <v>473.1090551329848</v>
       </c>
       <c r="H41">
-        <v>434.42363683147659</v>
+        <v>495.8121729549417</v>
       </c>
       <c r="I41">
-        <v>429.59463016949712</v>
+        <v>507.0172350778225</v>
       </c>
       <c r="J41">
-        <v>438.73747686885793</v>
+        <v>504.0239683094854</v>
       </c>
       <c r="K41">
-        <v>446.97082133911198</v>
+        <v>498.7607921921916</v>
       </c>
       <c r="L41">
-        <v>446.02983708934738</v>
+        <v>502.9645842465812</v>
       </c>
       <c r="M41">
-        <v>456.04917025324988</v>
+        <v>535.7371527102906</v>
       </c>
       <c r="N41">
-        <v>455.83015360207412</v>
+        <v>559.4119261326446</v>
       </c>
       <c r="O41">
-        <v>463.62202703772022</v>
+        <v>570.3616460700487</v>
       </c>
       <c r="P41">
-        <v>472.62406966754889</v>
+        <v>593.05326893983</v>
       </c>
       <c r="Q41">
-        <v>477.90609021557867</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>605.7561987116678</v>
+      </c>
+      <c r="R41">
+        <v>597.6212216223734</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>406.1679049970457</v>
+        <v>473.2433191329596</v>
       </c>
       <c r="C42">
-        <v>444.64061176740648</v>
-      </c>
-      <c r="D42" s="2">
-        <v>409.45951801527099</v>
+        <v>674.4628817661144</v>
+      </c>
+      <c r="D42">
+        <v>512.2953146471965</v>
       </c>
       <c r="E42">
-        <v>379.06297919261578</v>
+        <v>460.6796507531391</v>
       </c>
       <c r="F42">
-        <v>383.09856341390048</v>
+        <v>463.8371685594313</v>
       </c>
       <c r="G42">
-        <v>404.16862474044149</v>
+        <v>460.719336241736</v>
       </c>
       <c r="H42">
-        <v>429.94763074388311</v>
+        <v>490.7224799086035</v>
       </c>
       <c r="I42">
-        <v>413.60739943607763</v>
+        <v>482.9060657451664</v>
       </c>
       <c r="J42">
-        <v>417.88845741479298</v>
+        <v>484.3035385623297</v>
       </c>
       <c r="K42">
-        <v>408.37000474280973</v>
+        <v>505.6067027101736</v>
       </c>
       <c r="L42">
-        <v>393.56869946661908</v>
+        <v>536.0487607576398</v>
       </c>
       <c r="M42">
-        <v>399.66650289919733</v>
+        <v>561.8501582958803</v>
       </c>
       <c r="N42">
-        <v>405.29334202231797</v>
+        <v>568.6971655160987</v>
       </c>
       <c r="O42">
-        <v>404.14657165947301</v>
+        <v>572.6602141402332</v>
       </c>
       <c r="P42">
-        <v>413.48971557894208</v>
+        <v>582.1067443121683</v>
       </c>
       <c r="Q42">
-        <v>433.45423685341763</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>587.9673019102469</v>
+      </c>
+      <c r="R42">
+        <v>587.6545234917238</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>410.67760978145338</v>
+        <v>459.9439786697006</v>
       </c>
       <c r="C43">
-        <v>444.86080127593209</v>
-      </c>
-      <c r="D43" s="2">
-        <v>410.99214054279349</v>
+        <v>674.4628817661144</v>
+      </c>
+      <c r="D43">
+        <v>457.8142043151298</v>
       </c>
       <c r="E43">
-        <v>379.96177276325199</v>
+        <v>461.8065552896227</v>
       </c>
       <c r="F43">
-        <v>384.68990425721501</v>
+        <v>467.5811818547335</v>
       </c>
       <c r="G43">
-        <v>403.58546885841611</v>
+        <v>479.3255812566662</v>
       </c>
       <c r="H43">
-        <v>430.91747489320483</v>
+        <v>512.3733427243316</v>
       </c>
       <c r="I43">
-        <v>414.257997987355</v>
+        <v>501.6029804810199</v>
       </c>
       <c r="J43">
-        <v>418.28507624133221</v>
+        <v>490.6585201448275</v>
       </c>
       <c r="K43">
-        <v>412.9001965991128</v>
+        <v>483.5267609091238</v>
       </c>
       <c r="L43">
-        <v>405.45194033439611</v>
+        <v>512.1269717661559</v>
       </c>
       <c r="M43">
-        <v>408.12062578845428</v>
+        <v>510.4368165759739</v>
       </c>
       <c r="N43">
-        <v>413.20241956457431</v>
+        <v>526.2256249223036</v>
       </c>
       <c r="O43">
-        <v>409.13214702605922</v>
+        <v>531.7415208040026</v>
       </c>
       <c r="P43">
-        <v>411.76176174928548</v>
+        <v>528.775541871488</v>
       </c>
       <c r="Q43">
-        <v>426.38803270555781</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44">
-        <v>463.46715188845332</v>
-      </c>
-      <c r="C44">
-        <v>463.80548848667922</v>
-      </c>
-      <c r="D44">
-        <v>470.74499584956561</v>
-      </c>
-      <c r="E44">
-        <v>442.83497473136691</v>
-      </c>
-      <c r="F44">
-        <v>416.48481114095961</v>
-      </c>
-      <c r="G44">
-        <v>413.17237812019829</v>
-      </c>
-      <c r="H44">
-        <v>410.7426834744175</v>
-      </c>
-      <c r="I44">
-        <v>420.95332192925059</v>
-      </c>
-      <c r="J44">
-        <v>423.23330168276249</v>
-      </c>
-      <c r="K44">
-        <v>428.30766239180258</v>
-      </c>
-      <c r="L44">
-        <v>445.10778523212929</v>
-      </c>
-      <c r="M44">
-        <v>463.00242597367861</v>
-      </c>
-      <c r="N44">
-        <v>477.02942120033242</v>
-      </c>
-      <c r="O44">
-        <v>490.04302862188518</v>
-      </c>
-      <c r="P44">
-        <v>503.39207913609209</v>
-      </c>
-      <c r="Q44">
-        <v>525.25073346355816</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45">
-        <v>468.93876854000399</v>
-      </c>
-      <c r="C45">
-        <v>468.59645538857518</v>
-      </c>
-      <c r="D45">
-        <v>449.9227824182866</v>
-      </c>
-      <c r="E45">
-        <v>457.85977503827849</v>
-      </c>
-      <c r="F45">
-        <v>472.8570451339699</v>
-      </c>
-      <c r="G45">
-        <v>492.94506753389783</v>
-      </c>
-      <c r="H45">
-        <v>501.49663313299101</v>
-      </c>
-      <c r="I45">
-        <v>498.12589153693722</v>
-      </c>
-      <c r="J45">
-        <v>496.08882229858301</v>
-      </c>
-      <c r="K45">
-        <v>501.08322116908658</v>
-      </c>
-      <c r="L45">
-        <v>532.41872370492354</v>
-      </c>
-      <c r="M45">
-        <v>557.47821229954843</v>
-      </c>
-      <c r="N45">
-        <v>569.03109468187313</v>
-      </c>
-      <c r="O45">
-        <v>590.74444588482504</v>
-      </c>
-      <c r="P45">
-        <v>600.74219225880381</v>
-      </c>
-      <c r="Q45">
-        <v>593.09332947535813</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B46">
-        <v>470.76397499456039</v>
-      </c>
-      <c r="C46">
-        <v>510.77204900724769</v>
-      </c>
-      <c r="D46">
-        <v>459.08478619628971</v>
-      </c>
-      <c r="E46">
-        <v>459.85389327329159</v>
-      </c>
-      <c r="F46">
-        <v>459.23642880620042</v>
-      </c>
-      <c r="G46">
-        <v>486.59666603464302</v>
-      </c>
-      <c r="H46">
-        <v>480.4126550252987</v>
-      </c>
-      <c r="I46">
-        <v>479.96355206845652</v>
-      </c>
-      <c r="J46">
-        <v>499.96665811496081</v>
-      </c>
-      <c r="K46">
-        <v>531.15892528753341</v>
-      </c>
-      <c r="L46">
-        <v>559.92979199445949</v>
-      </c>
-      <c r="M46">
-        <v>568.38749401146242</v>
-      </c>
-      <c r="N46">
-        <v>570.78806169793449</v>
-      </c>
-      <c r="O46">
-        <v>580.56818993312868</v>
-      </c>
-      <c r="P46">
-        <v>586.38418027889247</v>
-      </c>
-      <c r="Q46">
-        <v>584.66958737257744</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47">
-        <v>462.75667467908181</v>
-      </c>
-      <c r="C47">
-        <v>459.03580488704449</v>
-      </c>
-      <c r="D47">
-        <v>464.29733502152249</v>
-      </c>
-      <c r="E47">
-        <v>470.65305989125272</v>
-      </c>
-      <c r="F47">
-        <v>481.95701314095811</v>
-      </c>
-      <c r="G47">
-        <v>515.37992495893002</v>
-      </c>
-      <c r="H47">
-        <v>503.65729134361288</v>
-      </c>
-      <c r="I47">
-        <v>493.10908325468358</v>
-      </c>
-      <c r="J47">
-        <v>485.60560385237142</v>
-      </c>
-      <c r="K47">
-        <v>514.22805259889185</v>
-      </c>
-      <c r="L47">
-        <v>513.5440070835798</v>
-      </c>
-      <c r="M47">
-        <v>528.83881326224889</v>
-      </c>
-      <c r="N47">
-        <v>536.03185799833693</v>
-      </c>
-      <c r="O47">
-        <v>532.67344251559973</v>
-      </c>
-      <c r="P47">
-        <v>531.85564760336922</v>
-      </c>
-      <c r="Q47">
-        <v>532.04610080570251</v>
+        <v>528.3117213154821</v>
+      </c>
+      <c r="R43">
+        <v>527.8198108561731</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q47">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>